--- a/12th Senate - audit results/All sittings in date order - finished or needs human check.xlsx
+++ b/12th Senate - audit results/All sittings in date order - finished or needs human check.xlsx
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="K16" s="6" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L16" s="6" t="n"/>
       <c r="M16" s="6" t="n"/>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="K22" s="6" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L22" s="6" t="n">
         <v>1</v>
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="K23" s="6" t="n">
-        <v>185</v>
+        <v>260</v>
       </c>
       <c r="L23" s="6" t="n"/>
       <c r="M23" s="6" t="n"/>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="K24" s="6" t="n">
-        <v>91</v>
+        <v>185</v>
       </c>
       <c r="L24" s="6" t="n">
         <v>3</v>
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="K25" s="6" t="n">
-        <v>164</v>
+        <v>250</v>
       </c>
       <c r="L25" s="6" t="n">
         <v>2</v>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="K26" s="6" t="n">
-        <v>199</v>
+        <v>279</v>
       </c>
       <c r="L26" s="6" t="n">
         <v>34</v>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="K28" s="6" t="n">
-        <v>401</v>
+        <v>503</v>
       </c>
       <c r="L28" s="6" t="n">
         <v>6</v>
@@ -1954,7 +1954,7 @@
         </is>
       </c>
       <c r="F31" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
@@ -1986,7 +1986,9 @@
       <c r="N31" s="6" t="n"/>
       <c r="O31" s="6" t="n"/>
       <c r="P31" s="6" t="n"/>
-      <c r="Q31" s="6" t="n"/>
+      <c r="Q31" s="6" t="n">
+        <v>2</v>
+      </c>
       <c r="R31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
@@ -3179,7 +3181,7 @@
         </is>
       </c>
       <c r="K52" s="6" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L52" s="6" t="n">
         <v>1</v>
@@ -3349,7 +3351,7 @@
         </is>
       </c>
       <c r="K55" s="6" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L55" s="6" t="n">
         <v>4</v>
@@ -3509,7 +3511,7 @@
         </is>
       </c>
       <c r="K58" s="6" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L58" s="6" t="n"/>
       <c r="M58" s="6" t="n"/>
@@ -4520,20 +4522,24 @@
           <t>14:30</t>
         </is>
       </c>
-      <c r="E76" s="11" t="inlineStr">
-        <is>
-          <t>Finished - no issues found</t>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>Needs human check</t>
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G76" s="9" t="inlineStr">
         <is>
           <t>2018-07-18-14-30-00 - Senate.json</t>
         </is>
       </c>
-      <c r="H76" s="6" t="inlineStr"/>
+      <c r="H76" s="9" t="inlineStr">
+        <is>
+          <t>2018-07-18-14-30-00 - Senate - flags.txt</t>
+        </is>
+      </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
           <t>2018-07-18 - Hansard Report - Wednesday, 18th July, 2018.pdf</t>
@@ -4552,7 +4558,9 @@
       <c r="N76" s="6" t="n"/>
       <c r="O76" s="6" t="n"/>
       <c r="P76" s="6" t="n"/>
-      <c r="Q76" s="6" t="n"/>
+      <c r="Q76" s="6" t="n">
+        <v>2</v>
+      </c>
       <c r="R76" s="10" t="inlineStr"/>
     </row>
     <row r="77">
@@ -4918,7 +4926,7 @@
         </is>
       </c>
       <c r="F83" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G83" s="9" t="inlineStr">
         <is>
@@ -4941,7 +4949,7 @@
         </is>
       </c>
       <c r="K83" s="6" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L83" s="6" t="n">
         <v>3</v>
@@ -4952,7 +4960,9 @@
       <c r="N83" s="6" t="n"/>
       <c r="O83" s="6" t="n"/>
       <c r="P83" s="6" t="n"/>
-      <c r="Q83" s="6" t="n"/>
+      <c r="Q83" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="R83" s="10" t="inlineStr"/>
     </row>
     <row r="84">
@@ -5111,7 +5121,7 @@
         </is>
       </c>
       <c r="K86" s="6" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L86" s="6" t="n">
         <v>1</v>
@@ -5383,7 +5393,7 @@
         </is>
       </c>
       <c r="K91" s="6" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L91" s="6" t="n"/>
       <c r="M91" s="6" t="n"/>
@@ -5651,7 +5661,7 @@
         </is>
       </c>
       <c r="K96" s="6" t="n">
-        <v>210</v>
+        <v>308</v>
       </c>
       <c r="L96" s="6" t="n">
         <v>4</v>
@@ -5713,7 +5723,7 @@
         </is>
       </c>
       <c r="K97" s="6" t="n">
-        <v>443</v>
+        <v>486</v>
       </c>
       <c r="L97" s="6" t="n">
         <v>1</v>
@@ -5775,7 +5785,7 @@
         </is>
       </c>
       <c r="K98" s="6" t="n">
-        <v>176</v>
+        <v>256</v>
       </c>
       <c r="L98" s="6" t="n"/>
       <c r="M98" s="6" t="n"/>
@@ -5885,7 +5895,7 @@
         </is>
       </c>
       <c r="K100" s="6" t="n">
-        <v>271</v>
+        <v>372</v>
       </c>
       <c r="L100" s="6" t="n">
         <v>6</v>
@@ -9245,7 +9255,7 @@
         </is>
       </c>
       <c r="K160" s="6" t="n">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="L160" s="6" t="n">
         <v>2</v>
@@ -9564,7 +9574,7 @@
         </is>
       </c>
       <c r="F166" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G166" s="9" t="inlineStr">
         <is>
@@ -9598,7 +9608,9 @@
       <c r="N166" s="6" t="n"/>
       <c r="O166" s="6" t="n"/>
       <c r="P166" s="6" t="n"/>
-      <c r="Q166" s="6" t="n"/>
+      <c r="Q166" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="R166" s="10" t="inlineStr"/>
     </row>
     <row r="167">
@@ -9643,7 +9655,7 @@
         </is>
       </c>
       <c r="K167" s="6" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L167" s="6" t="n"/>
       <c r="M167" s="6" t="n"/>
@@ -9751,7 +9763,7 @@
         </is>
       </c>
       <c r="K169" s="6" t="n">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="L169" s="6" t="n"/>
       <c r="M169" s="6" t="n">
@@ -11812,7 +11824,7 @@
         </is>
       </c>
       <c r="F207" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G207" s="9" t="inlineStr">
         <is>
@@ -11846,7 +11858,9 @@
       <c r="N207" s="6" t="n"/>
       <c r="O207" s="6" t="n"/>
       <c r="P207" s="6" t="n"/>
-      <c r="Q207" s="6" t="n"/>
+      <c r="Q207" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="R207" s="10" t="inlineStr"/>
     </row>
     <row r="208">
@@ -14594,20 +14608,24 @@
           <t>14:30</t>
         </is>
       </c>
-      <c r="E258" s="11" t="inlineStr">
-        <is>
-          <t>Finished - no issues found</t>
+      <c r="E258" s="8" t="inlineStr">
+        <is>
+          <t>Needs human check</t>
         </is>
       </c>
       <c r="F258" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G258" s="9" t="inlineStr">
         <is>
           <t>2020-07-21-14-30-00 - Senate.json</t>
         </is>
       </c>
-      <c r="H258" s="6" t="inlineStr"/>
+      <c r="H258" s="9" t="inlineStr">
+        <is>
+          <t>2020-07-21-14-30-00 - Senate - flags.txt</t>
+        </is>
+      </c>
       <c r="I258" s="6" t="inlineStr">
         <is>
           <t>2020-07-21 - Hansard Report - Tuesday, 21st July, 2020.pdf</t>
@@ -14626,7 +14644,9 @@
       <c r="N258" s="6" t="n"/>
       <c r="O258" s="6" t="n"/>
       <c r="P258" s="6" t="n"/>
-      <c r="Q258" s="6" t="n"/>
+      <c r="Q258" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="R258" s="10" t="inlineStr"/>
     </row>
     <row r="259">
@@ -15031,7 +15051,7 @@
         </is>
       </c>
       <c r="K265" s="6" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L265" s="6" t="n"/>
       <c r="M265" s="6" t="n"/>
@@ -15350,7 +15370,7 @@
         </is>
       </c>
       <c r="F271" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G271" s="9" t="inlineStr">
         <is>
@@ -15382,7 +15402,9 @@
       <c r="N271" s="6" t="n"/>
       <c r="O271" s="6" t="n"/>
       <c r="P271" s="6" t="n"/>
-      <c r="Q271" s="6" t="n"/>
+      <c r="Q271" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="R271" s="10" t="inlineStr"/>
     </row>
     <row r="272">
@@ -18554,20 +18576,24 @@
           <t>14:30</t>
         </is>
       </c>
-      <c r="E329" s="11" t="inlineStr">
-        <is>
-          <t>Finished - no issues found</t>
+      <c r="E329" s="8" t="inlineStr">
+        <is>
+          <t>Needs human check</t>
         </is>
       </c>
       <c r="F329" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G329" s="9" t="inlineStr">
         <is>
           <t>2021-07-07-14-30-00 - Senate.json</t>
         </is>
       </c>
-      <c r="H329" s="6" t="inlineStr"/>
+      <c r="H329" s="9" t="inlineStr">
+        <is>
+          <t>2021-07-07-14-30-00 - Senate - flags.txt</t>
+        </is>
+      </c>
       <c r="I329" s="6" t="inlineStr">
         <is>
           <t>2021-07-07 - Hansard Report - Wednesday, 7th July, 2021.pdf</t>
@@ -18586,7 +18612,9 @@
       <c r="N329" s="6" t="n"/>
       <c r="O329" s="6" t="n"/>
       <c r="P329" s="6" t="n"/>
-      <c r="Q329" s="6" t="n"/>
+      <c r="Q329" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="R329" s="10" t="inlineStr"/>
     </row>
     <row r="330">
@@ -23568,7 +23596,7 @@
         </is>
       </c>
       <c r="F423" s="6" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G423" s="9" t="inlineStr">
         <is>
@@ -23602,7 +23630,9 @@
       </c>
       <c r="O423" s="6" t="n"/>
       <c r="P423" s="6" t="n"/>
-      <c r="Q423" s="6" t="n"/>
+      <c r="Q423" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="R423" s="10" t="inlineStr"/>
     </row>
     <row r="424">
@@ -24074,856 +24104,859 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J75" r:id="rId177"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J76" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J77" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J78" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J79" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J80" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J81" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J82" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J83" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J84" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J85" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J86" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J87" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J88" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J89" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J90" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J91" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J92" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J93" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J94" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J95" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J96" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J97" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J98" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J99" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J100" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J101" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J102" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J103" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J104" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J105" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G106" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J106" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J107" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J108" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J109" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H110" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J110" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J111" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J112" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J113" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G114" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J114" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J115" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J116" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J117" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J118" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J119" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J120" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J121" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J122" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G123" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J123" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J124" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J125" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J126" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G127" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J127" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J128" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J129" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J130" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J131" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J132" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G133" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J133" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J134" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J135" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J136" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J137" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G138" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J138" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G139" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J139" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G140" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J140" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G141" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J141" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G142" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J142" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G143" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J143" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G144" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J144" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G145" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J145" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J146" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J147" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G148" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J148" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G149" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J149" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G150" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J150" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J151" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J152" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G153" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H153" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J153" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H154" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J154" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J155" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G156" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J156" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G157" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J157" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J158" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G159" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J159" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G160" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H160" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J160" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G161" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J161" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G162" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H162" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J162" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G163" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J163" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G164" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H164" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J164" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G165" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J165" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G166" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H166" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J166" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G167" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J167" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G168" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J168" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G169" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J169" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G170" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J170" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G171" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H171" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J171" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G172" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J172" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G173" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H173" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J173" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G174" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H174" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J174" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G175" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H175" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J175" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G176" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H176" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J176" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G177" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J177" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G178" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H178" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J178" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G179" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H179" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J179" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G180" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H180" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J180" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G181" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J181" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G182" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J182" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G183" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J183" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G184" r:id="rId454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H184" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J184" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G185" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J185" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G186" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H186" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J186" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G187" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H187" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J187" r:id="rId464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G188" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J188" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G189" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H189" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J189" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G190" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J190" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G191" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J191" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G192" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H192" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J192" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G193" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J193" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G194" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J194" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G195" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J195" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G196" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J196" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G197" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H197" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J197" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G198" r:id="rId488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J198" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G199" r:id="rId490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J199" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G200" r:id="rId492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J200" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G201" r:id="rId494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J201" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G202" r:id="rId496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J202" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G203" r:id="rId498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J203" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G204" r:id="rId500"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J204" r:id="rId501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G205" r:id="rId502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J205" r:id="rId503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G206" r:id="rId504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J206" r:id="rId505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G207" r:id="rId506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H207" r:id="rId507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J207" r:id="rId508"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G208" r:id="rId509"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J208" r:id="rId510"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G209" r:id="rId511"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H209" r:id="rId512"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J209" r:id="rId513"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G210" r:id="rId514"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J210" r:id="rId515"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G211" r:id="rId516"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J211" r:id="rId517"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G212" r:id="rId518"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J212" r:id="rId519"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G213" r:id="rId520"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J213" r:id="rId521"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G214" r:id="rId522"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J214" r:id="rId523"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G215" r:id="rId524"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J215" r:id="rId525"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G216" r:id="rId526"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H216" r:id="rId527"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J216" r:id="rId528"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G217" r:id="rId529"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J217" r:id="rId530"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G218" r:id="rId531"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H218" r:id="rId532"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J218" r:id="rId533"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G219" r:id="rId534"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H219" r:id="rId535"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J219" r:id="rId536"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G220" r:id="rId537"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J220" r:id="rId538"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G221" r:id="rId539"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J221" r:id="rId540"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G222" r:id="rId541"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H222" r:id="rId542"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J222" r:id="rId543"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G223" r:id="rId544"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J223" r:id="rId545"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G224" r:id="rId546"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J224" r:id="rId547"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G225" r:id="rId548"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H225" r:id="rId549"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J225" r:id="rId550"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G226" r:id="rId551"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J226" r:id="rId552"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G227" r:id="rId553"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J227" r:id="rId554"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G228" r:id="rId555"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J228" r:id="rId556"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G229" r:id="rId557"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J229" r:id="rId558"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G230" r:id="rId559"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J230" r:id="rId560"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G231" r:id="rId561"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J231" r:id="rId562"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G232" r:id="rId563"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H232" r:id="rId564"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J232" r:id="rId565"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G233" r:id="rId566"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J233" r:id="rId567"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G234" r:id="rId568"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J234" r:id="rId569"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G235" r:id="rId570"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J235" r:id="rId571"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G236" r:id="rId572"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H236" r:id="rId573"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J236" r:id="rId574"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G237" r:id="rId575"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J237" r:id="rId576"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G238" r:id="rId577"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J238" r:id="rId578"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G239" r:id="rId579"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H239" r:id="rId580"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J239" r:id="rId581"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G240" r:id="rId582"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H240" r:id="rId583"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J240" r:id="rId584"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G241" r:id="rId585"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J241" r:id="rId586"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G242" r:id="rId587"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H242" r:id="rId588"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J242" r:id="rId589"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G243" r:id="rId590"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J243" r:id="rId591"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G244" r:id="rId592"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H244" r:id="rId593"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J244" r:id="rId594"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G245" r:id="rId595"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J245" r:id="rId596"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G246" r:id="rId597"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J246" r:id="rId598"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G247" r:id="rId599"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J247" r:id="rId600"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G248" r:id="rId601"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J248" r:id="rId602"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G249" r:id="rId603"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H249" r:id="rId604"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J249" r:id="rId605"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G250" r:id="rId606"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J250" r:id="rId607"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G251" r:id="rId608"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H251" r:id="rId609"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J251" r:id="rId610"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G252" r:id="rId611"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J252" r:id="rId612"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G253" r:id="rId613"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J253" r:id="rId614"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G254" r:id="rId615"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H254" r:id="rId616"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J254" r:id="rId617"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G255" r:id="rId618"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H255" r:id="rId619"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J255" r:id="rId620"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G256" r:id="rId621"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J256" r:id="rId622"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G257" r:id="rId623"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J257" r:id="rId624"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G258" r:id="rId625"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J258" r:id="rId626"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G259" r:id="rId627"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H259" r:id="rId628"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J259" r:id="rId629"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G260" r:id="rId630"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H260" r:id="rId631"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J260" r:id="rId632"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G261" r:id="rId633"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H261" r:id="rId634"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J261" r:id="rId635"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G262" r:id="rId636"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H262" r:id="rId637"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J262" r:id="rId638"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G263" r:id="rId639"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H263" r:id="rId640"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J263" r:id="rId641"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G264" r:id="rId642"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H264" r:id="rId643"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J264" r:id="rId644"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G265" r:id="rId645"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J265" r:id="rId646"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G266" r:id="rId647"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J266" r:id="rId648"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G267" r:id="rId649"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H267" r:id="rId650"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J267" r:id="rId651"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G268" r:id="rId652"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H268" r:id="rId653"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J268" r:id="rId654"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G269" r:id="rId655"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H269" r:id="rId656"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J269" r:id="rId657"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G270" r:id="rId658"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H270" r:id="rId659"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J270" r:id="rId660"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G271" r:id="rId661"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H271" r:id="rId662"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J271" r:id="rId663"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G272" r:id="rId664"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H272" r:id="rId665"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J272" r:id="rId666"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G273" r:id="rId667"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J273" r:id="rId668"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G274" r:id="rId669"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H274" r:id="rId670"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J274" r:id="rId671"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G275" r:id="rId672"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J275" r:id="rId673"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G276" r:id="rId674"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J276" r:id="rId675"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G277" r:id="rId676"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J277" r:id="rId677"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G278" r:id="rId678"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H278" r:id="rId679"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J278" r:id="rId680"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G279" r:id="rId681"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H279" r:id="rId682"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J279" r:id="rId683"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G280" r:id="rId684"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H280" r:id="rId685"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J280" r:id="rId686"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G281" r:id="rId687"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J281" r:id="rId688"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G282" r:id="rId689"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H282" r:id="rId690"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J282" r:id="rId691"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G283" r:id="rId692"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J283" r:id="rId693"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G284" r:id="rId694"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H284" r:id="rId695"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J284" r:id="rId696"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G285" r:id="rId697"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J285" r:id="rId698"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G286" r:id="rId699"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H286" r:id="rId700"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J286" r:id="rId701"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G287" r:id="rId702"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J287" r:id="rId703"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G288" r:id="rId704"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H288" r:id="rId705"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J288" r:id="rId706"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G289" r:id="rId707"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H289" r:id="rId708"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J289" r:id="rId709"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G290" r:id="rId710"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H290" r:id="rId711"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J290" r:id="rId712"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G291" r:id="rId713"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H291" r:id="rId714"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J291" r:id="rId715"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G292" r:id="rId716"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J292" r:id="rId717"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G293" r:id="rId718"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J293" r:id="rId719"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G294" r:id="rId720"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J294" r:id="rId721"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G295" r:id="rId722"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H295" r:id="rId723"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J295" r:id="rId724"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G296" r:id="rId725"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J296" r:id="rId726"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G297" r:id="rId727"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H297" r:id="rId728"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J297" r:id="rId729"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G298" r:id="rId730"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J298" r:id="rId731"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G299" r:id="rId732"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J299" r:id="rId733"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G300" r:id="rId734"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H300" r:id="rId735"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J300" r:id="rId736"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G301" r:id="rId737"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H301" r:id="rId738"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J301" r:id="rId739"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G302" r:id="rId740"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J302" r:id="rId741"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G303" r:id="rId742"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J303" r:id="rId743"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G304" r:id="rId744"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J304" r:id="rId745"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G305" r:id="rId746"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J305" r:id="rId747"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G306" r:id="rId748"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H306" r:id="rId749"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J306" r:id="rId750"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G307" r:id="rId751"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J307" r:id="rId752"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G308" r:id="rId753"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H308" r:id="rId754"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J308" r:id="rId755"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G309" r:id="rId756"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J309" r:id="rId757"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G310" r:id="rId758"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J310" r:id="rId759"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G311" r:id="rId760"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J311" r:id="rId761"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G312" r:id="rId762"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J312" r:id="rId763"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G313" r:id="rId764"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J313" r:id="rId765"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G314" r:id="rId766"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J314" r:id="rId767"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G315" r:id="rId768"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J315" r:id="rId769"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G316" r:id="rId770"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J316" r:id="rId771"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G317" r:id="rId772"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J317" r:id="rId773"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G318" r:id="rId774"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J318" r:id="rId775"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G319" r:id="rId776"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H319" r:id="rId777"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J319" r:id="rId778"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G320" r:id="rId779"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H320" r:id="rId780"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J320" r:id="rId781"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G321" r:id="rId782"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J321" r:id="rId783"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G322" r:id="rId784"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J322" r:id="rId785"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G323" r:id="rId786"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J323" r:id="rId787"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G324" r:id="rId788"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H324" r:id="rId789"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J324" r:id="rId790"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G325" r:id="rId791"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H325" r:id="rId792"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J325" r:id="rId793"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G326" r:id="rId794"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J326" r:id="rId795"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G327" r:id="rId796"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J327" r:id="rId797"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G328" r:id="rId798"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H328" r:id="rId799"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J328" r:id="rId800"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G329" r:id="rId801"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J329" r:id="rId802"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G330" r:id="rId803"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J330" r:id="rId804"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G331" r:id="rId805"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J331" r:id="rId806"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G332" r:id="rId807"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J332" r:id="rId808"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G333" r:id="rId809"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J333" r:id="rId810"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G334" r:id="rId811"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J334" r:id="rId812"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G335" r:id="rId813"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J335" r:id="rId814"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G336" r:id="rId815"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J336" r:id="rId816"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G337" r:id="rId817"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J337" r:id="rId818"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G338" r:id="rId819"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H338" r:id="rId820"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J338" r:id="rId821"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G339" r:id="rId822"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H339" r:id="rId823"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J339" r:id="rId824"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G340" r:id="rId825"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H340" r:id="rId826"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J340" r:id="rId827"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G341" r:id="rId828"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H341" r:id="rId829"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J341" r:id="rId830"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G342" r:id="rId831"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J342" r:id="rId832"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G343" r:id="rId833"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J343" r:id="rId834"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G344" r:id="rId835"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H344" r:id="rId836"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J344" r:id="rId837"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G345" r:id="rId838"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H345" r:id="rId839"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J345" r:id="rId840"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G346" r:id="rId841"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J346" r:id="rId842"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G347" r:id="rId843"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J347" r:id="rId844"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G348" r:id="rId845"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J348" r:id="rId846"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G349" r:id="rId847"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J349" r:id="rId848"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G350" r:id="rId849"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H350" r:id="rId850"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J350" r:id="rId851"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G351" r:id="rId852"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J351" r:id="rId853"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G352" r:id="rId854"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J352" r:id="rId855"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G353" r:id="rId856"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H353" r:id="rId857"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J353" r:id="rId858"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G354" r:id="rId859"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J354" r:id="rId860"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G355" r:id="rId861"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J355" r:id="rId862"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G356" r:id="rId863"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J356" r:id="rId864"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G357" r:id="rId865"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J357" r:id="rId866"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G358" r:id="rId867"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J358" r:id="rId868"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G359" r:id="rId869"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J359" r:id="rId870"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G360" r:id="rId871"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J360" r:id="rId872"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G361" r:id="rId873"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H361" r:id="rId874"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J361" r:id="rId875"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G362" r:id="rId876"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J362" r:id="rId877"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G363" r:id="rId878"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J363" r:id="rId879"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G364" r:id="rId880"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J364" r:id="rId881"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G365" r:id="rId882"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J365" r:id="rId883"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G366" r:id="rId884"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J366" r:id="rId885"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G367" r:id="rId886"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J367" r:id="rId887"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G368" r:id="rId888"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J368" r:id="rId889"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G369" r:id="rId890"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J369" r:id="rId891"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G370" r:id="rId892"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J370" r:id="rId893"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G371" r:id="rId894"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J371" r:id="rId895"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G372" r:id="rId896"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J372" r:id="rId897"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G373" r:id="rId898"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J373" r:id="rId899"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G374" r:id="rId900"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H374" r:id="rId901"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J374" r:id="rId902"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G375" r:id="rId903"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J375" r:id="rId904"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G376" r:id="rId905"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J376" r:id="rId906"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G377" r:id="rId907"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J377" r:id="rId908"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G378" r:id="rId909"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J378" r:id="rId910"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G379" r:id="rId911"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J379" r:id="rId912"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G380" r:id="rId913"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H380" r:id="rId914"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J380" r:id="rId915"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G381" r:id="rId916"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J381" r:id="rId917"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G382" r:id="rId918"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J382" r:id="rId919"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G383" r:id="rId920"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J383" r:id="rId921"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G384" r:id="rId922"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H384" r:id="rId923"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J384" r:id="rId924"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G385" r:id="rId925"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J385" r:id="rId926"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G386" r:id="rId927"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J386" r:id="rId928"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G387" r:id="rId929"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J387" r:id="rId930"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G388" r:id="rId931"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J388" r:id="rId932"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G389" r:id="rId933"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J389" r:id="rId934"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G390" r:id="rId935"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J390" r:id="rId936"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G391" r:id="rId937"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J391" r:id="rId938"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G392" r:id="rId939"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J392" r:id="rId940"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G393" r:id="rId941"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J393" r:id="rId942"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G394" r:id="rId943"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J394" r:id="rId944"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G395" r:id="rId945"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J395" r:id="rId946"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G396" r:id="rId947"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J396" r:id="rId948"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G397" r:id="rId949"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H397" r:id="rId950"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J397" r:id="rId951"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G398" r:id="rId952"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J398" r:id="rId953"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G399" r:id="rId954"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H399" r:id="rId955"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J399" r:id="rId956"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G400" r:id="rId957"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J400" r:id="rId958"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G401" r:id="rId959"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H401" r:id="rId960"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J401" r:id="rId961"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G402" r:id="rId962"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H402" r:id="rId963"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J402" r:id="rId964"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G403" r:id="rId965"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J403" r:id="rId966"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G404" r:id="rId967"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J404" r:id="rId968"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G405" r:id="rId969"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J405" r:id="rId970"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G406" r:id="rId971"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H406" r:id="rId972"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J406" r:id="rId973"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G407" r:id="rId974"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H407" r:id="rId975"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J407" r:id="rId976"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G408" r:id="rId977"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J408" r:id="rId978"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G409" r:id="rId979"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H409" r:id="rId980"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J409" r:id="rId981"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G410" r:id="rId982"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J410" r:id="rId983"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G411" r:id="rId984"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J411" r:id="rId985"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G412" r:id="rId986"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J412" r:id="rId987"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G413" r:id="rId988"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J413" r:id="rId989"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G414" r:id="rId990"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J414" r:id="rId991"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G415" r:id="rId992"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J415" r:id="rId993"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G416" r:id="rId994"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J416" r:id="rId995"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G417" r:id="rId996"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J417" r:id="rId997"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G418" r:id="rId998"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J418" r:id="rId999"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G419" r:id="rId1000"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J419" r:id="rId1001"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G420" r:id="rId1002"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J420" r:id="rId1003"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G421" r:id="rId1004"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J421" r:id="rId1005"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G422" r:id="rId1006"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H422" r:id="rId1007"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J422" r:id="rId1008"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G423" r:id="rId1009"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H423" r:id="rId1010"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J423" r:id="rId1011"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G424" r:id="rId1012"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H424" r:id="rId1013"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J424" r:id="rId1014"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G425" r:id="rId1015"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H425" r:id="rId1016"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J425" r:id="rId1017"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G426" r:id="rId1018"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J426" r:id="rId1019"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G427" r:id="rId1020"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H427" r:id="rId1021"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J427" r:id="rId1022"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G428" r:id="rId1023"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J428" r:id="rId1024"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J76" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J77" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J78" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J79" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J80" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J81" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J82" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J83" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J84" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J85" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J86" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J87" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J88" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J89" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J90" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J91" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J92" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J93" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J94" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J95" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J96" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J97" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J98" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J99" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J100" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J101" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J102" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J103" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J104" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J105" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G106" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J106" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J107" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J108" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J109" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H110" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J110" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J111" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J112" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J113" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G114" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J114" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J115" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J116" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J117" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J118" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J119" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J120" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J121" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J122" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G123" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J123" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J124" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J125" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J126" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G127" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J127" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J128" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J129" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J130" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J131" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J132" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G133" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J133" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J134" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J135" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J136" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J137" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G138" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J138" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G139" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J139" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G140" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J140" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G141" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J141" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G142" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J142" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G143" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J143" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G144" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J144" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G145" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J145" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J146" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J147" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G148" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J148" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G149" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J149" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G150" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J150" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J151" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J152" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G153" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H153" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J153" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H154" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J154" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J155" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G156" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J156" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G157" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J157" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J158" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G159" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J159" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G160" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H160" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J160" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G161" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J161" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G162" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H162" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J162" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G163" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J163" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G164" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H164" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J164" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G165" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J165" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G166" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H166" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J166" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G167" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J167" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G168" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J168" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G169" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J169" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G170" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J170" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G171" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H171" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J171" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G172" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J172" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G173" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H173" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J173" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G174" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H174" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J174" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G175" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H175" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J175" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G176" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H176" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J176" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G177" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J177" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G178" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H178" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J178" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G179" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H179" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J179" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G180" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H180" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J180" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G181" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J181" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G182" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J182" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G183" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J183" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G184" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H184" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J184" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G185" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J185" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G186" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H186" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J186" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G187" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H187" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J187" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G188" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J188" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G189" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H189" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J189" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G190" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J190" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G191" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J191" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G192" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H192" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J192" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G193" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J193" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G194" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J194" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G195" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J195" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G196" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J196" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G197" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H197" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J197" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G198" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J198" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G199" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J199" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G200" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J200" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G201" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J201" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G202" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J202" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G203" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J203" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G204" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J204" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G205" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J205" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G206" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J206" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G207" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H207" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J207" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G208" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J208" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G209" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H209" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J209" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G210" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J210" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G211" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J211" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G212" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J212" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G213" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J213" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G214" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J214" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G215" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J215" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G216" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H216" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J216" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G217" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J217" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G218" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H218" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J218" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G219" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H219" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J219" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G220" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J220" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G221" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J221" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G222" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H222" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J222" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G223" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J223" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G224" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J224" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G225" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H225" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J225" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G226" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J226" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G227" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J227" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G228" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J228" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G229" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J229" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G230" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J230" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G231" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J231" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G232" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H232" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J232" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G233" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J233" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G234" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J234" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G235" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J235" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G236" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H236" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J236" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G237" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J237" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G238" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J238" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G239" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H239" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J239" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G240" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H240" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J240" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G241" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J241" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G242" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H242" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J242" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G243" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J243" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G244" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H244" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J244" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G245" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J245" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G246" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J246" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G247" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J247" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G248" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J248" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G249" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H249" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J249" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G250" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J250" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G251" r:id="rId609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H251" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J251" r:id="rId611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G252" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J252" r:id="rId613"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G253" r:id="rId614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J253" r:id="rId615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G254" r:id="rId616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H254" r:id="rId617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J254" r:id="rId618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G255" r:id="rId619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H255" r:id="rId620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J255" r:id="rId621"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G256" r:id="rId622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J256" r:id="rId623"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G257" r:id="rId624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J257" r:id="rId625"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G258" r:id="rId626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H258" r:id="rId627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J258" r:id="rId628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G259" r:id="rId629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H259" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J259" r:id="rId631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G260" r:id="rId632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H260" r:id="rId633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J260" r:id="rId634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G261" r:id="rId635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H261" r:id="rId636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J261" r:id="rId637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G262" r:id="rId638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H262" r:id="rId639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J262" r:id="rId640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G263" r:id="rId641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H263" r:id="rId642"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J263" r:id="rId643"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G264" r:id="rId644"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H264" r:id="rId645"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J264" r:id="rId646"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G265" r:id="rId647"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J265" r:id="rId648"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G266" r:id="rId649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J266" r:id="rId650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G267" r:id="rId651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H267" r:id="rId652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J267" r:id="rId653"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G268" r:id="rId654"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H268" r:id="rId655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J268" r:id="rId656"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G269" r:id="rId657"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H269" r:id="rId658"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J269" r:id="rId659"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G270" r:id="rId660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H270" r:id="rId661"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J270" r:id="rId662"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G271" r:id="rId663"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H271" r:id="rId664"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J271" r:id="rId665"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G272" r:id="rId666"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H272" r:id="rId667"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J272" r:id="rId668"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G273" r:id="rId669"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J273" r:id="rId670"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G274" r:id="rId671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H274" r:id="rId672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J274" r:id="rId673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G275" r:id="rId674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J275" r:id="rId675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G276" r:id="rId676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J276" r:id="rId677"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G277" r:id="rId678"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J277" r:id="rId679"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G278" r:id="rId680"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H278" r:id="rId681"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J278" r:id="rId682"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G279" r:id="rId683"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H279" r:id="rId684"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J279" r:id="rId685"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G280" r:id="rId686"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H280" r:id="rId687"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J280" r:id="rId688"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G281" r:id="rId689"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J281" r:id="rId690"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G282" r:id="rId691"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H282" r:id="rId692"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J282" r:id="rId693"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G283" r:id="rId694"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J283" r:id="rId695"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G284" r:id="rId696"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H284" r:id="rId697"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J284" r:id="rId698"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G285" r:id="rId699"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J285" r:id="rId700"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G286" r:id="rId701"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H286" r:id="rId702"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J286" r:id="rId703"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G287" r:id="rId704"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J287" r:id="rId705"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G288" r:id="rId706"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H288" r:id="rId707"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J288" r:id="rId708"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G289" r:id="rId709"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H289" r:id="rId710"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J289" r:id="rId711"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G290" r:id="rId712"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H290" r:id="rId713"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J290" r:id="rId714"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G291" r:id="rId715"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H291" r:id="rId716"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J291" r:id="rId717"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G292" r:id="rId718"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J292" r:id="rId719"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G293" r:id="rId720"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J293" r:id="rId721"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G294" r:id="rId722"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J294" r:id="rId723"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G295" r:id="rId724"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H295" r:id="rId725"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J295" r:id="rId726"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G296" r:id="rId727"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J296" r:id="rId728"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G297" r:id="rId729"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H297" r:id="rId730"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J297" r:id="rId731"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G298" r:id="rId732"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J298" r:id="rId733"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G299" r:id="rId734"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J299" r:id="rId735"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G300" r:id="rId736"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H300" r:id="rId737"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J300" r:id="rId738"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G301" r:id="rId739"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H301" r:id="rId740"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J301" r:id="rId741"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G302" r:id="rId742"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J302" r:id="rId743"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G303" r:id="rId744"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J303" r:id="rId745"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G304" r:id="rId746"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J304" r:id="rId747"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G305" r:id="rId748"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J305" r:id="rId749"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G306" r:id="rId750"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H306" r:id="rId751"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J306" r:id="rId752"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G307" r:id="rId753"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J307" r:id="rId754"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G308" r:id="rId755"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H308" r:id="rId756"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J308" r:id="rId757"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G309" r:id="rId758"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J309" r:id="rId759"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G310" r:id="rId760"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J310" r:id="rId761"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G311" r:id="rId762"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J311" r:id="rId763"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G312" r:id="rId764"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J312" r:id="rId765"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G313" r:id="rId766"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J313" r:id="rId767"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G314" r:id="rId768"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J314" r:id="rId769"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G315" r:id="rId770"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J315" r:id="rId771"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G316" r:id="rId772"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J316" r:id="rId773"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G317" r:id="rId774"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J317" r:id="rId775"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G318" r:id="rId776"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J318" r:id="rId777"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G319" r:id="rId778"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H319" r:id="rId779"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J319" r:id="rId780"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G320" r:id="rId781"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H320" r:id="rId782"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J320" r:id="rId783"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G321" r:id="rId784"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J321" r:id="rId785"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G322" r:id="rId786"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J322" r:id="rId787"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G323" r:id="rId788"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J323" r:id="rId789"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G324" r:id="rId790"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H324" r:id="rId791"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J324" r:id="rId792"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G325" r:id="rId793"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H325" r:id="rId794"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J325" r:id="rId795"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G326" r:id="rId796"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J326" r:id="rId797"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G327" r:id="rId798"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J327" r:id="rId799"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G328" r:id="rId800"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H328" r:id="rId801"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J328" r:id="rId802"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G329" r:id="rId803"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H329" r:id="rId804"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J329" r:id="rId805"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G330" r:id="rId806"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J330" r:id="rId807"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G331" r:id="rId808"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J331" r:id="rId809"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G332" r:id="rId810"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J332" r:id="rId811"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G333" r:id="rId812"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J333" r:id="rId813"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G334" r:id="rId814"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J334" r:id="rId815"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G335" r:id="rId816"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J335" r:id="rId817"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G336" r:id="rId818"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J336" r:id="rId819"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G337" r:id="rId820"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J337" r:id="rId821"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G338" r:id="rId822"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H338" r:id="rId823"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J338" r:id="rId824"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G339" r:id="rId825"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H339" r:id="rId826"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J339" r:id="rId827"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G340" r:id="rId828"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H340" r:id="rId829"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J340" r:id="rId830"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G341" r:id="rId831"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H341" r:id="rId832"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J341" r:id="rId833"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G342" r:id="rId834"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J342" r:id="rId835"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G343" r:id="rId836"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J343" r:id="rId837"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G344" r:id="rId838"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H344" r:id="rId839"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J344" r:id="rId840"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G345" r:id="rId841"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H345" r:id="rId842"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J345" r:id="rId843"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G346" r:id="rId844"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J346" r:id="rId845"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G347" r:id="rId846"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J347" r:id="rId847"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G348" r:id="rId848"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J348" r:id="rId849"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G349" r:id="rId850"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J349" r:id="rId851"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G350" r:id="rId852"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H350" r:id="rId853"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J350" r:id="rId854"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G351" r:id="rId855"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J351" r:id="rId856"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G352" r:id="rId857"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J352" r:id="rId858"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G353" r:id="rId859"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H353" r:id="rId860"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J353" r:id="rId861"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G354" r:id="rId862"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J354" r:id="rId863"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G355" r:id="rId864"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J355" r:id="rId865"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G356" r:id="rId866"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J356" r:id="rId867"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G357" r:id="rId868"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J357" r:id="rId869"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G358" r:id="rId870"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J358" r:id="rId871"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G359" r:id="rId872"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J359" r:id="rId873"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G360" r:id="rId874"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J360" r:id="rId875"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G361" r:id="rId876"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H361" r:id="rId877"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J361" r:id="rId878"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G362" r:id="rId879"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J362" r:id="rId880"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G363" r:id="rId881"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J363" r:id="rId882"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G364" r:id="rId883"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J364" r:id="rId884"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G365" r:id="rId885"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J365" r:id="rId886"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G366" r:id="rId887"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J366" r:id="rId888"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G367" r:id="rId889"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J367" r:id="rId890"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G368" r:id="rId891"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J368" r:id="rId892"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G369" r:id="rId893"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J369" r:id="rId894"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G370" r:id="rId895"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J370" r:id="rId896"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G371" r:id="rId897"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J371" r:id="rId898"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G372" r:id="rId899"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J372" r:id="rId900"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G373" r:id="rId901"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J373" r:id="rId902"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G374" r:id="rId903"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H374" r:id="rId904"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J374" r:id="rId905"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G375" r:id="rId906"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J375" r:id="rId907"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G376" r:id="rId908"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J376" r:id="rId909"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G377" r:id="rId910"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J377" r:id="rId911"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G378" r:id="rId912"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J378" r:id="rId913"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G379" r:id="rId914"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J379" r:id="rId915"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G380" r:id="rId916"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H380" r:id="rId917"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J380" r:id="rId918"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G381" r:id="rId919"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J381" r:id="rId920"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G382" r:id="rId921"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J382" r:id="rId922"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G383" r:id="rId923"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J383" r:id="rId924"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G384" r:id="rId925"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H384" r:id="rId926"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J384" r:id="rId927"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G385" r:id="rId928"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J385" r:id="rId929"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G386" r:id="rId930"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J386" r:id="rId931"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G387" r:id="rId932"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J387" r:id="rId933"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G388" r:id="rId934"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J388" r:id="rId935"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G389" r:id="rId936"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J389" r:id="rId937"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G390" r:id="rId938"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J390" r:id="rId939"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G391" r:id="rId940"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J391" r:id="rId941"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G392" r:id="rId942"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J392" r:id="rId943"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G393" r:id="rId944"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J393" r:id="rId945"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G394" r:id="rId946"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J394" r:id="rId947"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G395" r:id="rId948"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J395" r:id="rId949"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G396" r:id="rId950"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J396" r:id="rId951"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G397" r:id="rId952"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H397" r:id="rId953"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J397" r:id="rId954"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G398" r:id="rId955"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J398" r:id="rId956"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G399" r:id="rId957"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H399" r:id="rId958"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J399" r:id="rId959"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G400" r:id="rId960"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J400" r:id="rId961"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G401" r:id="rId962"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H401" r:id="rId963"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J401" r:id="rId964"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G402" r:id="rId965"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H402" r:id="rId966"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J402" r:id="rId967"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G403" r:id="rId968"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J403" r:id="rId969"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G404" r:id="rId970"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J404" r:id="rId971"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G405" r:id="rId972"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J405" r:id="rId973"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G406" r:id="rId974"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H406" r:id="rId975"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J406" r:id="rId976"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G407" r:id="rId977"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H407" r:id="rId978"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J407" r:id="rId979"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G408" r:id="rId980"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J408" r:id="rId981"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G409" r:id="rId982"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H409" r:id="rId983"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J409" r:id="rId984"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G410" r:id="rId985"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J410" r:id="rId986"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G411" r:id="rId987"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J411" r:id="rId988"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G412" r:id="rId989"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J412" r:id="rId990"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G413" r:id="rId991"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J413" r:id="rId992"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G414" r:id="rId993"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J414" r:id="rId994"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G415" r:id="rId995"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J415" r:id="rId996"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G416" r:id="rId997"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J416" r:id="rId998"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G417" r:id="rId999"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J417" r:id="rId1000"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G418" r:id="rId1001"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J418" r:id="rId1002"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G419" r:id="rId1003"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J419" r:id="rId1004"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G420" r:id="rId1005"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J420" r:id="rId1006"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G421" r:id="rId1007"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J421" r:id="rId1008"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G422" r:id="rId1009"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H422" r:id="rId1010"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J422" r:id="rId1011"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G423" r:id="rId1012"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H423" r:id="rId1013"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J423" r:id="rId1014"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G424" r:id="rId1015"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H424" r:id="rId1016"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J424" r:id="rId1017"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G425" r:id="rId1018"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H425" r:id="rId1019"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J425" r:id="rId1020"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G426" r:id="rId1021"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J426" r:id="rId1022"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G427" r:id="rId1023"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H427" r:id="rId1024"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J427" r:id="rId1025"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G428" r:id="rId1026"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J428" r:id="rId1027"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1025"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1028"/>
   </tableParts>
 </worksheet>
 </file>
--- a/12th Senate - audit results/All sittings in date order - finished or needs human check.xlsx
+++ b/12th Senate - audit results/All sittings in date order - finished or needs human check.xlsx
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="K22" s="6" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="L22" s="6" t="n">
         <v>1</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="K24" s="6" t="n">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="L24" s="6" t="n">
         <v>3</v>
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="K25" s="6" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L25" s="6" t="n">
         <v>2</v>
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="K27" s="6" t="n">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="L27" s="6" t="n"/>
       <c r="M27" s="6" t="n"/>
@@ -2551,7 +2551,7 @@
         </is>
       </c>
       <c r="K41" s="6" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="L41" s="6" t="n">
         <v>7</v>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="L42" s="6" t="n"/>
       <c r="M42" s="6" t="n"/>
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="K43" s="6" t="n">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="L43" s="6" t="n"/>
       <c r="M43" s="6" t="n"/>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="K44" s="6" t="n">
-        <v>331</v>
+        <v>352</v>
       </c>
       <c r="L44" s="6" t="n"/>
       <c r="M44" s="6" t="n"/>
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="K48" s="6" t="n">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="L48" s="6" t="n"/>
       <c r="M48" s="6" t="n"/>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="K49" s="6" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="L49" s="6" t="n"/>
       <c r="M49" s="6" t="n"/>
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="K51" s="6" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="L51" s="6" t="n"/>
       <c r="M51" s="6" t="n"/>
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="K52" s="6" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L52" s="6" t="n">
         <v>1</v>
@@ -3241,7 +3241,7 @@
         </is>
       </c>
       <c r="K53" s="6" t="n">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="L53" s="6" t="n"/>
       <c r="M53" s="6" t="n">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="K55" s="6" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L55" s="6" t="n">
         <v>4</v>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="K67" s="6" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L67" s="6" t="n"/>
       <c r="M67" s="6" t="n">
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="K68" s="6" t="n">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L68" s="6" t="n"/>
       <c r="M68" s="6" t="n">
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="K85" s="6" t="n">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="L85" s="6" t="n"/>
       <c r="M85" s="6" t="n"/>
@@ -18491,7 +18491,7 @@
         </is>
       </c>
       <c r="K327" s="6" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="L327" s="6" t="n"/>
       <c r="M327" s="6" t="n"/>
@@ -20337,7 +20337,7 @@
         </is>
       </c>
       <c r="K361" s="6" t="n">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="L361" s="6" t="n"/>
       <c r="M361" s="6" t="n">
@@ -20599,7 +20599,7 @@
         </is>
       </c>
       <c r="K366" s="6" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L366" s="6" t="n"/>
       <c r="M366" s="6" t="n"/>
@@ -20911,7 +20911,7 @@
         </is>
       </c>
       <c r="K372" s="6" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L372" s="6" t="n"/>
       <c r="M372" s="6" t="n"/>
@@ -23853,7 +23853,7 @@
         </is>
       </c>
       <c r="K427" s="6" t="n">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="L427" s="6" t="n">
         <v>1</v>

--- a/12th Senate - audit results/All sittings in date order - finished or needs human check.xlsx
+++ b/12th Senate - audit results/All sittings in date order - finished or needs human check.xlsx
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="K15" s="6" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L15" s="6" t="n"/>
       <c r="M15" s="6" t="n"/>
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="K17" s="6" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L17" s="6" t="n"/>
       <c r="M17" s="6" t="n"/>
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="K19" s="6" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="L19" s="6" t="n">
         <v>1</v>
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="K20" s="6" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L20" s="6" t="n">
         <v>3</v>
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="K21" s="6" t="n">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="L21" s="6" t="n">
         <v>1</v>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="K22" s="6" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L22" s="6" t="n">
         <v>1</v>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="K28" s="6" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L28" s="6" t="n">
         <v>6</v>
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="K29" s="6" t="n">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="L29" s="6" t="n"/>
       <c r="M29" s="6" t="n">
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="K31" s="6" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L31" s="6" t="n"/>
       <c r="M31" s="6" t="n">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="K32" s="6" t="n">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="L32" s="6" t="n"/>
       <c r="M32" s="6" t="n"/>
@@ -2375,7 +2375,7 @@
         </is>
       </c>
       <c r="K38" s="6" t="n">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="L38" s="6" t="n">
         <v>9</v>
@@ -2493,7 +2493,7 @@
         </is>
       </c>
       <c r="K40" s="6" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L40" s="6" t="n"/>
       <c r="M40" s="6" t="n"/>
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="K45" s="6" t="n">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="L45" s="6" t="n">
         <v>5</v>
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="K46" s="6" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L46" s="6" t="n"/>
       <c r="M46" s="6" t="n"/>
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="K48" s="6" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L48" s="6" t="n"/>
       <c r="M48" s="6" t="n"/>
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="K55" s="6" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L55" s="6" t="n">
         <v>4</v>
@@ -3407,7 +3407,7 @@
         </is>
       </c>
       <c r="K56" s="6" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L56" s="6" t="n"/>
       <c r="M56" s="6" t="n"/>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="K61" s="6" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L61" s="6" t="n">
         <v>3</v>
@@ -4771,7 +4771,7 @@
         </is>
       </c>
       <c r="K80" s="6" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L80" s="6" t="n"/>
       <c r="M80" s="6" t="n"/>
@@ -5229,7 +5229,7 @@
         </is>
       </c>
       <c r="K88" s="6" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L88" s="6" t="n"/>
       <c r="M88" s="6" t="n"/>
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="K96" s="6" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L96" s="6" t="n">
         <v>4</v>
@@ -5723,7 +5723,7 @@
         </is>
       </c>
       <c r="K97" s="6" t="n">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="L97" s="6" t="n">
         <v>1</v>
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="K105" s="6" t="n">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="L105" s="6" t="n"/>
       <c r="M105" s="6" t="n"/>
@@ -6551,7 +6551,7 @@
         </is>
       </c>
       <c r="K112" s="6" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="L112" s="6" t="n"/>
       <c r="M112" s="6" t="n"/>
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="K113" s="6" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L113" s="6" t="n"/>
       <c r="M113" s="6" t="n"/>
@@ -8979,7 +8979,7 @@
         </is>
       </c>
       <c r="K155" s="6" t="n">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="L155" s="6" t="n"/>
       <c r="M155" s="6" t="n"/>
@@ -9255,7 +9255,7 @@
         </is>
       </c>
       <c r="K160" s="6" t="n">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="L160" s="6" t="n">
         <v>2</v>
@@ -11531,7 +11531,7 @@
         </is>
       </c>
       <c r="K201" s="6" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L201" s="6" t="n"/>
       <c r="M201" s="6" t="n"/>
@@ -12837,7 +12837,7 @@
         </is>
       </c>
       <c r="K225" s="6" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L225" s="6" t="n">
         <v>4</v>
@@ -13101,7 +13101,7 @@
         </is>
       </c>
       <c r="K230" s="6" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="L230" s="6" t="n"/>
       <c r="M230" s="6" t="n"/>
@@ -13477,7 +13477,7 @@
         </is>
       </c>
       <c r="K237" s="6" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L237" s="6" t="n"/>
       <c r="M237" s="6" t="n"/>
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="K248" s="6" t="n">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="L248" s="6" t="n"/>
       <c r="M248" s="6" t="n"/>
@@ -16125,7 +16125,7 @@
         </is>
       </c>
       <c r="K284" s="6" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L284" s="6" t="n">
         <v>1</v>
@@ -17245,7 +17245,7 @@
         </is>
       </c>
       <c r="K304" s="6" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L304" s="6" t="n"/>
       <c r="M304" s="6" t="n"/>
@@ -19143,7 +19143,7 @@
         </is>
       </c>
       <c r="K339" s="6" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L339" s="6" t="n"/>
       <c r="M339" s="6" t="n"/>
@@ -20177,7 +20177,7 @@
         </is>
       </c>
       <c r="K358" s="6" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="L358" s="6" t="n"/>
       <c r="M358" s="6" t="n"/>
@@ -20547,7 +20547,7 @@
         </is>
       </c>
       <c r="K365" s="6" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L365" s="6" t="n"/>
       <c r="M365" s="6" t="n"/>
@@ -20599,7 +20599,7 @@
         </is>
       </c>
       <c r="K366" s="6" t="n">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="L366" s="6" t="n"/>
       <c r="M366" s="6" t="n"/>
@@ -20807,7 +20807,7 @@
         </is>
       </c>
       <c r="K370" s="6" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L370" s="6" t="n"/>
       <c r="M370" s="6" t="n"/>
@@ -20859,7 +20859,7 @@
         </is>
       </c>
       <c r="K371" s="6" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L371" s="6" t="n"/>
       <c r="M371" s="6" t="n"/>
@@ -21173,7 +21173,7 @@
         </is>
       </c>
       <c r="K377" s="6" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L377" s="6" t="n"/>
       <c r="M377" s="6" t="n"/>
@@ -21803,7 +21803,7 @@
         </is>
       </c>
       <c r="K389" s="6" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L389" s="6" t="n"/>
       <c r="M389" s="6" t="n"/>
@@ -22103,7 +22103,7 @@
         </is>
       </c>
       <c r="K395" s="6" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L395" s="6" t="n"/>
       <c r="M395" s="6" t="n"/>
@@ -22155,7 +22155,7 @@
         </is>
       </c>
       <c r="K396" s="6" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="L396" s="6" t="n"/>
       <c r="M396" s="6" t="n"/>

--- a/12th Senate - audit results/All sittings in date order - finished or needs human check.xlsx
+++ b/12th Senate - audit results/All sittings in date order - finished or needs human check.xlsx
@@ -2375,7 +2375,7 @@
         </is>
       </c>
       <c r="K38" s="6" t="n">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="L38" s="6" t="n">
         <v>9</v>
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="K46" s="6" t="n">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="L46" s="6" t="n"/>
       <c r="M46" s="6" t="n"/>
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="K48" s="6" t="n">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="L48" s="6" t="n"/>
       <c r="M48" s="6" t="n"/>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="K49" s="6" t="n">
-        <v>704</v>
+        <v>664</v>
       </c>
       <c r="L49" s="6" t="n"/>
       <c r="M49" s="6" t="n"/>
@@ -3241,7 +3241,7 @@
         </is>
       </c>
       <c r="K53" s="6" t="n">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="L53" s="6" t="n"/>
       <c r="M53" s="6" t="n">
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="K57" s="6" t="n">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="L57" s="6" t="n"/>
       <c r="M57" s="6" t="n"/>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="K60" s="6" t="n">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="L60" s="6" t="n"/>
       <c r="M60" s="6" t="n"/>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="K62" s="6" t="n">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="L62" s="6" t="n">
         <v>1</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="K64" s="6" t="n">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="L64" s="6" t="n">
         <v>3</v>
@@ -3925,7 +3925,7 @@
         </is>
       </c>
       <c r="K65" s="6" t="n">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="L65" s="6" t="n"/>
       <c r="M65" s="6" t="n"/>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="K67" s="6" t="n">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="L67" s="6" t="n"/>
       <c r="M67" s="6" t="n">
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="K68" s="6" t="n">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="L68" s="6" t="n"/>
       <c r="M68" s="6" t="n">
@@ -4151,7 +4151,7 @@
         </is>
       </c>
       <c r="K69" s="6" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="L69" s="6" t="n"/>
       <c r="M69" s="6" t="n"/>
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="K72" s="6" t="n">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="L72" s="6" t="n"/>
       <c r="M72" s="6" t="n">
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="K73" s="6" t="n">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="L73" s="6" t="n">
         <v>3</v>
@@ -4495,7 +4495,7 @@
         </is>
       </c>
       <c r="K75" s="6" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="L75" s="6" t="n"/>
       <c r="M75" s="6" t="n"/>
@@ -4713,7 +4713,7 @@
         </is>
       </c>
       <c r="K79" s="6" t="n">
-        <v>410</v>
+        <v>388</v>
       </c>
       <c r="L79" s="6" t="n"/>
       <c r="M79" s="6" t="n"/>
@@ -4771,7 +4771,7 @@
         </is>
       </c>
       <c r="K80" s="6" t="n">
-        <v>306</v>
+        <v>284</v>
       </c>
       <c r="L80" s="6" t="n"/>
       <c r="M80" s="6" t="n"/>
@@ -5011,7 +5011,7 @@
         </is>
       </c>
       <c r="K84" s="6" t="n">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L84" s="6" t="n">
         <v>1</v>
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="K85" s="6" t="n">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L85" s="6" t="n"/>
       <c r="M85" s="6" t="n"/>
@@ -5229,7 +5229,7 @@
         </is>
       </c>
       <c r="K88" s="6" t="n">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="L88" s="6" t="n"/>
       <c r="M88" s="6" t="n"/>
@@ -5505,7 +5505,7 @@
         </is>
       </c>
       <c r="K93" s="6" t="n">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="L93" s="6" t="n">
         <v>14</v>
@@ -5557,7 +5557,7 @@
         </is>
       </c>
       <c r="K94" s="6" t="n">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="L94" s="6" t="n"/>
       <c r="M94" s="6" t="n"/>
@@ -5605,7 +5605,7 @@
         </is>
       </c>
       <c r="K95" s="6" t="n">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="L95" s="6" t="n"/>
       <c r="M95" s="6" t="n"/>
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="K96" s="6" t="n">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="L96" s="6" t="n">
         <v>4</v>
@@ -5785,7 +5785,7 @@
         </is>
       </c>
       <c r="K98" s="6" t="n">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="L98" s="6" t="n"/>
       <c r="M98" s="6" t="n"/>
@@ -5839,7 +5839,7 @@
         </is>
       </c>
       <c r="K99" s="6" t="n">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="L99" s="6" t="n"/>
       <c r="M99" s="6" t="n"/>
@@ -5895,7 +5895,7 @@
         </is>
       </c>
       <c r="K100" s="6" t="n">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="L100" s="6" t="n">
         <v>6</v>
@@ -6015,7 +6015,7 @@
         </is>
       </c>
       <c r="K102" s="6" t="n">
-        <v>446</v>
+        <v>422</v>
       </c>
       <c r="L102" s="6" t="n"/>
       <c r="M102" s="6" t="n"/>
@@ -6129,7 +6129,7 @@
         </is>
       </c>
       <c r="K104" s="6" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="L104" s="6" t="n"/>
       <c r="M104" s="6" t="n"/>
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="K105" s="6" t="n">
-        <v>552</v>
+        <v>516</v>
       </c>
       <c r="L105" s="6" t="n"/>
       <c r="M105" s="6" t="n"/>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="K106" s="6" t="n">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="L106" s="6" t="n"/>
       <c r="M106" s="6" t="n"/>
@@ -6285,7 +6285,7 @@
         </is>
       </c>
       <c r="K107" s="6" t="n">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="L107" s="6" t="n"/>
       <c r="M107" s="6" t="n"/>
@@ -6337,7 +6337,7 @@
         </is>
       </c>
       <c r="K108" s="6" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="L108" s="6" t="n"/>
       <c r="M108" s="6" t="n"/>
@@ -6389,7 +6389,7 @@
         </is>
       </c>
       <c r="K109" s="6" t="n">
-        <v>196</v>
+        <v>160</v>
       </c>
       <c r="L109" s="6" t="n"/>
       <c r="M109" s="6" t="n"/>
@@ -6499,7 +6499,7 @@
         </is>
       </c>
       <c r="K111" s="6" t="n">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="L111" s="6" t="n"/>
       <c r="M111" s="6" t="n"/>
@@ -6551,7 +6551,7 @@
         </is>
       </c>
       <c r="K112" s="6" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="L112" s="6" t="n"/>
       <c r="M112" s="6" t="n"/>
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="K113" s="6" t="n">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="L113" s="6" t="n"/>
       <c r="M113" s="6" t="n"/>
@@ -6659,7 +6659,7 @@
         </is>
       </c>
       <c r="K114" s="6" t="n">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="L114" s="6" t="n"/>
       <c r="M114" s="6" t="n">
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="K115" s="6" t="n">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="L115" s="6" t="n"/>
       <c r="M115" s="6" t="n"/>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="K116" s="6" t="n">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="L116" s="6" t="n"/>
       <c r="M116" s="6" t="n"/>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="K118" s="6" t="n">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L118" s="6" t="n"/>
       <c r="M118" s="6" t="n"/>
@@ -6951,7 +6951,7 @@
         </is>
       </c>
       <c r="K119" s="6" t="n">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="L119" s="6" t="n"/>
       <c r="M119" s="6" t="n"/>
@@ -7007,7 +7007,7 @@
         </is>
       </c>
       <c r="K120" s="6" t="n">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="L120" s="6" t="n"/>
       <c r="M120" s="6" t="n">
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="K121" s="6" t="n">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="L121" s="6" t="n">
         <v>6</v>
@@ -7173,7 +7173,7 @@
         </is>
       </c>
       <c r="K123" s="6" t="n">
-        <v>1574</v>
+        <v>1469</v>
       </c>
       <c r="L123" s="6" t="n"/>
       <c r="M123" s="6" t="n"/>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="K124" s="6" t="n">
-        <v>837</v>
+        <v>812</v>
       </c>
       <c r="L124" s="6" t="n"/>
       <c r="M124" s="6" t="n">
@@ -7407,7 +7407,7 @@
         </is>
       </c>
       <c r="K127" s="6" t="n">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="L127" s="6" t="n"/>
       <c r="M127" s="6" t="n">
@@ -7517,7 +7517,7 @@
         </is>
       </c>
       <c r="K129" s="6" t="n">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="L129" s="6" t="n">
         <v>16</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="K131" s="6" t="n">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="L131" s="6" t="n"/>
       <c r="M131" s="6" t="n"/>
@@ -7693,7 +7693,7 @@
         </is>
       </c>
       <c r="K132" s="6" t="n">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="L132" s="6" t="n"/>
       <c r="M132" s="6" t="n"/>
@@ -7745,7 +7745,7 @@
         </is>
       </c>
       <c r="K133" s="6" t="n">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="L133" s="6" t="n"/>
       <c r="M133" s="6" t="n"/>
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="K135" s="6" t="n">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="L135" s="6" t="n"/>
       <c r="M135" s="6" t="n"/>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="K137" s="6" t="n">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="L137" s="6" t="n"/>
       <c r="M137" s="6" t="n"/>
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="K140" s="6" t="n">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="L140" s="6" t="n">
         <v>1</v>
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="K141" s="6" t="n">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="L141" s="6" t="n">
         <v>5</v>
@@ -8481,7 +8481,7 @@
         </is>
       </c>
       <c r="K146" s="6" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L146" s="6" t="n"/>
       <c r="M146" s="6" t="n">
@@ -8583,7 +8583,7 @@
         </is>
       </c>
       <c r="K148" s="6" t="n">
-        <v>234</v>
+        <v>204</v>
       </c>
       <c r="L148" s="6" t="n"/>
       <c r="M148" s="6" t="n"/>
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="K150" s="6" t="n">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="L150" s="6" t="n"/>
       <c r="M150" s="6" t="n"/>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="K151" s="6" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L151" s="6" t="n"/>
       <c r="M151" s="6" t="n"/>
@@ -8861,7 +8861,7 @@
         </is>
       </c>
       <c r="K153" s="6" t="n">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="L153" s="6" t="n">
         <v>1</v>
@@ -8979,7 +8979,7 @@
         </is>
       </c>
       <c r="K155" s="6" t="n">
-        <v>655</v>
+        <v>564</v>
       </c>
       <c r="L155" s="6" t="n"/>
       <c r="M155" s="6" t="n"/>
@@ -9035,7 +9035,7 @@
         </is>
       </c>
       <c r="K156" s="6" t="n">
-        <v>375</v>
+        <v>351</v>
       </c>
       <c r="L156" s="6" t="n"/>
       <c r="M156" s="6" t="n"/>
@@ -9141,7 +9141,7 @@
         </is>
       </c>
       <c r="K158" s="6" t="n">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="L158" s="6" t="n"/>
       <c r="M158" s="6" t="n"/>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="K159" s="6" t="n">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="L159" s="6" t="n"/>
       <c r="M159" s="6" t="n">
@@ -9255,7 +9255,7 @@
         </is>
       </c>
       <c r="K160" s="6" t="n">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="L160" s="6" t="n">
         <v>2</v>
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="F161" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G161" s="9" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         </is>
       </c>
       <c r="K161" s="6" t="n">
-        <v>582</v>
+        <v>557</v>
       </c>
       <c r="L161" s="6" t="n"/>
       <c r="M161" s="6" t="n">
@@ -9326,7 +9326,9 @@
       </c>
       <c r="O161" s="6" t="n"/>
       <c r="P161" s="6" t="n"/>
-      <c r="Q161" s="6" t="n"/>
+      <c r="Q161" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="R161" s="10" t="inlineStr"/>
     </row>
     <row r="162">
@@ -9375,7 +9377,7 @@
         </is>
       </c>
       <c r="K162" s="6" t="n">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="L162" s="6" t="n"/>
       <c r="M162" s="6" t="n">
@@ -9485,7 +9487,7 @@
         </is>
       </c>
       <c r="K164" s="6" t="n">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="L164" s="6" t="n">
         <v>14</v>
@@ -9763,7 +9765,7 @@
         </is>
       </c>
       <c r="K169" s="6" t="n">
-        <v>752</v>
+        <v>677</v>
       </c>
       <c r="L169" s="6" t="n"/>
       <c r="M169" s="6" t="n">
@@ -9993,7 +9995,7 @@
         </is>
       </c>
       <c r="K173" s="6" t="n">
-        <v>417</v>
+        <v>404</v>
       </c>
       <c r="L173" s="6" t="n">
         <v>4</v>
@@ -10113,7 +10115,7 @@
         </is>
       </c>
       <c r="K175" s="6" t="n">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="L175" s="6" t="n">
         <v>1</v>
@@ -10231,7 +10233,7 @@
         </is>
       </c>
       <c r="K177" s="6" t="n">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="L177" s="6" t="n"/>
       <c r="M177" s="6" t="n"/>
@@ -10287,7 +10289,7 @@
         </is>
       </c>
       <c r="K178" s="6" t="n">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="L178" s="6" t="n"/>
       <c r="M178" s="6" t="n"/>
@@ -10561,7 +10563,7 @@
         </is>
       </c>
       <c r="K183" s="6" t="n">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="L183" s="6" t="n"/>
       <c r="M183" s="6" t="n"/>
@@ -10665,7 +10667,7 @@
         </is>
       </c>
       <c r="K185" s="6" t="n">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="L185" s="6" t="n"/>
       <c r="M185" s="6" t="n"/>
@@ -10995,7 +10997,7 @@
         </is>
       </c>
       <c r="K191" s="6" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="L191" s="6" t="n"/>
       <c r="M191" s="6" t="n"/>
@@ -11159,7 +11161,7 @@
         </is>
       </c>
       <c r="K194" s="6" t="n">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="L194" s="6" t="n"/>
       <c r="M194" s="6" t="n"/>
@@ -11687,7 +11689,7 @@
         </is>
       </c>
       <c r="K204" s="6" t="n">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="L204" s="6" t="n"/>
       <c r="M204" s="6" t="n"/>
@@ -11791,7 +11793,7 @@
         </is>
       </c>
       <c r="K206" s="6" t="n">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="L206" s="6" t="n"/>
       <c r="M206" s="6" t="n"/>
@@ -11847,7 +11849,7 @@
         </is>
       </c>
       <c r="K207" s="6" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L207" s="6" t="n">
         <v>4</v>
@@ -12071,7 +12073,7 @@
         </is>
       </c>
       <c r="K211" s="6" t="n">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="L211" s="6" t="n"/>
       <c r="M211" s="6" t="n"/>
@@ -12123,7 +12125,7 @@
         </is>
       </c>
       <c r="K212" s="6" t="n">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="L212" s="6" t="n"/>
       <c r="M212" s="6" t="n"/>
@@ -12279,7 +12281,7 @@
         </is>
       </c>
       <c r="K215" s="6" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="L215" s="6" t="n"/>
       <c r="M215" s="6" t="n"/>
@@ -12445,7 +12447,7 @@
         </is>
       </c>
       <c r="K218" s="6" t="n">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="L218" s="6" t="n"/>
       <c r="M218" s="6" t="n"/>
@@ -12781,7 +12783,7 @@
         </is>
       </c>
       <c r="K224" s="6" t="n">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="L224" s="6" t="n"/>
       <c r="M224" s="6" t="n"/>
@@ -12837,7 +12839,7 @@
         </is>
       </c>
       <c r="K225" s="6" t="n">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="L225" s="6" t="n">
         <v>4</v>
@@ -12945,7 +12947,7 @@
         </is>
       </c>
       <c r="K227" s="6" t="n">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="L227" s="6" t="n"/>
       <c r="M227" s="6" t="n"/>
@@ -13049,7 +13051,7 @@
         </is>
       </c>
       <c r="K229" s="6" t="n">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="L229" s="6" t="n"/>
       <c r="M229" s="6" t="n"/>
@@ -13315,7 +13317,7 @@
         </is>
       </c>
       <c r="K234" s="6" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="L234" s="6" t="n"/>
       <c r="M234" s="6" t="n"/>
@@ -13423,7 +13425,7 @@
         </is>
       </c>
       <c r="K236" s="6" t="n">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="L236" s="6" t="n"/>
       <c r="M236" s="6" t="n">
@@ -13477,7 +13479,7 @@
         </is>
       </c>
       <c r="K237" s="6" t="n">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="L237" s="6" t="n"/>
       <c r="M237" s="6" t="n"/>
@@ -13585,7 +13587,7 @@
         </is>
       </c>
       <c r="K239" s="6" t="n">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="L239" s="6" t="n">
         <v>14</v>
@@ -13813,7 +13815,7 @@
         </is>
       </c>
       <c r="K243" s="6" t="n">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="L243" s="6" t="n"/>
       <c r="M243" s="6" t="n"/>
@@ -13869,7 +13871,7 @@
         </is>
       </c>
       <c r="K244" s="6" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L244" s="6" t="n"/>
       <c r="M244" s="6" t="n"/>
@@ -14031,7 +14033,7 @@
         </is>
       </c>
       <c r="K247" s="6" t="n">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="L247" s="6" t="n"/>
       <c r="M247" s="6" t="n"/>
@@ -14083,7 +14085,7 @@
         </is>
       </c>
       <c r="K248" s="6" t="n">
-        <v>577</v>
+        <v>555</v>
       </c>
       <c r="L248" s="6" t="n"/>
       <c r="M248" s="6" t="n"/>
@@ -14139,7 +14141,7 @@
         </is>
       </c>
       <c r="K249" s="6" t="n">
-        <v>574</v>
+        <v>555</v>
       </c>
       <c r="L249" s="6" t="n">
         <v>4</v>
@@ -14251,7 +14253,7 @@
         </is>
       </c>
       <c r="K251" s="6" t="n">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="L251" s="6" t="n"/>
       <c r="M251" s="6" t="n"/>
@@ -14305,7 +14307,7 @@
         </is>
       </c>
       <c r="K252" s="6" t="n">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="L252" s="6" t="n"/>
       <c r="M252" s="6" t="n"/>
@@ -14357,7 +14359,7 @@
         </is>
       </c>
       <c r="K253" s="6" t="n">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L253" s="6" t="n"/>
       <c r="M253" s="6" t="n"/>
@@ -14637,7 +14639,7 @@
         </is>
       </c>
       <c r="K258" s="6" t="n">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="L258" s="6" t="n"/>
       <c r="M258" s="6" t="n"/>
@@ -14695,7 +14697,7 @@
         </is>
       </c>
       <c r="K259" s="6" t="n">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="L259" s="6" t="n"/>
       <c r="M259" s="6" t="n">
@@ -14753,7 +14755,7 @@
         </is>
       </c>
       <c r="K260" s="6" t="n">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="L260" s="6" t="n"/>
       <c r="M260" s="6" t="n"/>
@@ -14811,7 +14813,7 @@
         </is>
       </c>
       <c r="K261" s="6" t="n">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="L261" s="6" t="n"/>
       <c r="M261" s="6" t="n"/>
@@ -15051,7 +15053,7 @@
         </is>
       </c>
       <c r="K265" s="6" t="n">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="L265" s="6" t="n"/>
       <c r="M265" s="6" t="n"/>
@@ -15217,7 +15219,7 @@
         </is>
       </c>
       <c r="K268" s="6" t="n">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="L268" s="6" t="n">
         <v>2</v>
@@ -15511,7 +15513,7 @@
         </is>
       </c>
       <c r="K273" s="6" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="L273" s="6" t="n"/>
       <c r="M273" s="6" t="n"/>
@@ -15905,7 +15907,7 @@
         </is>
       </c>
       <c r="K280" s="6" t="n">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="L280" s="6" t="n"/>
       <c r="M280" s="6" t="n"/>
@@ -16015,7 +16017,7 @@
         </is>
       </c>
       <c r="K282" s="6" t="n">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="L282" s="6" t="n"/>
       <c r="M282" s="6" t="n"/>
@@ -16125,7 +16127,7 @@
         </is>
       </c>
       <c r="K284" s="6" t="n">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="L284" s="6" t="n">
         <v>1</v>
@@ -16442,7 +16444,7 @@
         </is>
       </c>
       <c r="F290" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G290" s="9" t="inlineStr">
         <is>
@@ -16465,7 +16467,7 @@
         </is>
       </c>
       <c r="K290" s="6" t="n">
-        <v>1510</v>
+        <v>1506</v>
       </c>
       <c r="L290" s="6" t="n">
         <v>8</v>
@@ -16478,7 +16480,9 @@
       </c>
       <c r="O290" s="6" t="n"/>
       <c r="P290" s="6" t="n"/>
-      <c r="Q290" s="6" t="n"/>
+      <c r="Q290" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="R290" s="10" t="inlineStr"/>
     </row>
     <row r="291">
@@ -16527,7 +16531,7 @@
         </is>
       </c>
       <c r="K291" s="6" t="n">
-        <v>536</v>
+        <v>526</v>
       </c>
       <c r="L291" s="6" t="n"/>
       <c r="M291" s="6" t="n"/>
@@ -16587,7 +16591,7 @@
         </is>
       </c>
       <c r="K292" s="6" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="L292" s="6" t="n"/>
       <c r="M292" s="6" t="n"/>
@@ -16967,7 +16971,7 @@
         </is>
       </c>
       <c r="K299" s="6" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L299" s="6" t="n"/>
       <c r="M299" s="6" t="n"/>
@@ -17245,7 +17249,7 @@
         </is>
       </c>
       <c r="K304" s="6" t="n">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="L304" s="6" t="n"/>
       <c r="M304" s="6" t="n"/>
@@ -17297,7 +17301,7 @@
         </is>
       </c>
       <c r="K305" s="6" t="n">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="L305" s="6" t="n"/>
       <c r="M305" s="6" t="n"/>
@@ -17729,7 +17733,7 @@
         </is>
       </c>
       <c r="K313" s="6" t="n">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L313" s="6" t="n"/>
       <c r="M313" s="6" t="n"/>
@@ -17989,7 +17993,7 @@
         </is>
       </c>
       <c r="K318" s="6" t="n">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="L318" s="6" t="n"/>
       <c r="M318" s="6" t="n"/>
@@ -18491,7 +18495,7 @@
         </is>
       </c>
       <c r="K327" s="6" t="n">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="L327" s="6" t="n"/>
       <c r="M327" s="6" t="n"/>
@@ -18711,7 +18715,7 @@
         </is>
       </c>
       <c r="K331" s="6" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="L331" s="6" t="n"/>
       <c r="M331" s="6" t="n"/>
@@ -19079,7 +19083,7 @@
         </is>
       </c>
       <c r="K338" s="6" t="n">
-        <v>1100</v>
+        <v>984</v>
       </c>
       <c r="L338" s="6" t="n">
         <v>7</v>
@@ -19182,7 +19186,7 @@
         </is>
       </c>
       <c r="F340" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G340" s="9" t="inlineStr">
         <is>
@@ -19205,7 +19209,7 @@
         </is>
       </c>
       <c r="K340" s="6" t="n">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="L340" s="6" t="n"/>
       <c r="M340" s="6" t="n"/>
@@ -19213,7 +19217,7 @@
       <c r="O340" s="6" t="n"/>
       <c r="P340" s="6" t="n"/>
       <c r="Q340" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R340" s="10" t="inlineStr">
         <is>
@@ -19373,7 +19377,7 @@
         </is>
       </c>
       <c r="K343" s="6" t="n">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L343" s="6" t="n"/>
       <c r="M343" s="6" t="n"/>
@@ -19487,7 +19491,7 @@
         </is>
       </c>
       <c r="K345" s="6" t="n">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="L345" s="6" t="n"/>
       <c r="M345" s="6" t="n"/>
@@ -19863,7 +19867,7 @@
         </is>
       </c>
       <c r="K352" s="6" t="n">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="L352" s="6" t="n"/>
       <c r="M352" s="6" t="n"/>
@@ -20073,7 +20077,7 @@
         </is>
       </c>
       <c r="K356" s="6" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="L356" s="6" t="n"/>
       <c r="M356" s="6" t="n"/>
@@ -20229,7 +20233,7 @@
         </is>
       </c>
       <c r="K359" s="6" t="n">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="L359" s="6" t="n"/>
       <c r="M359" s="6" t="n"/>
@@ -20337,7 +20341,7 @@
         </is>
       </c>
       <c r="K361" s="6" t="n">
-        <v>926</v>
+        <v>916</v>
       </c>
       <c r="L361" s="6" t="n"/>
       <c r="M361" s="6" t="n">
@@ -20391,7 +20395,7 @@
         </is>
       </c>
       <c r="K362" s="6" t="n">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="L362" s="6" t="n"/>
       <c r="M362" s="6" t="n"/>
@@ -20755,7 +20759,7 @@
         </is>
       </c>
       <c r="K369" s="6" t="n">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="L369" s="6" t="n"/>
       <c r="M369" s="6" t="n"/>
@@ -21015,7 +21019,7 @@
         </is>
       </c>
       <c r="K374" s="6" t="n">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="L374" s="6" t="n"/>
       <c r="M374" s="6" t="n"/>
@@ -21173,7 +21177,7 @@
         </is>
       </c>
       <c r="K377" s="6" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="L377" s="6" t="n"/>
       <c r="M377" s="6" t="n"/>
@@ -21387,7 +21391,7 @@
         </is>
       </c>
       <c r="K381" s="6" t="n">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="L381" s="6" t="n"/>
       <c r="M381" s="6" t="n"/>
@@ -21951,7 +21955,7 @@
         </is>
       </c>
       <c r="K392" s="6" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="L392" s="6" t="n"/>
       <c r="M392" s="6" t="n"/>
@@ -22003,7 +22007,7 @@
         </is>
       </c>
       <c r="K393" s="6" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L393" s="6" t="n"/>
       <c r="M393" s="6" t="n"/>
@@ -22103,7 +22107,7 @@
         </is>
       </c>
       <c r="K395" s="6" t="n">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="L395" s="6" t="n"/>
       <c r="M395" s="6" t="n"/>
@@ -22937,7 +22941,7 @@
         </is>
       </c>
       <c r="K410" s="6" t="n">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="L410" s="6" t="n"/>
       <c r="M410" s="6" t="n"/>
@@ -23093,7 +23097,7 @@
         </is>
       </c>
       <c r="K413" s="6" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="L413" s="6" t="n"/>
       <c r="M413" s="6" t="n"/>
@@ -23197,7 +23201,7 @@
         </is>
       </c>
       <c r="K415" s="6" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L415" s="6" t="n"/>
       <c r="M415" s="6" t="n"/>
@@ -23301,7 +23305,7 @@
         </is>
       </c>
       <c r="K417" s="6" t="n">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L417" s="6" t="n"/>
       <c r="M417" s="6" t="n"/>
@@ -23353,7 +23357,7 @@
         </is>
       </c>
       <c r="K418" s="6" t="n">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="L418" s="6" t="n"/>
       <c r="M418" s="6" t="n"/>
@@ -23853,7 +23857,7 @@
         </is>
       </c>
       <c r="K427" s="6" t="n">
-        <v>1059</v>
+        <v>1051</v>
       </c>
       <c r="L427" s="6" t="n">
         <v>1</v>

--- a/12th Senate - audit results/All sittings in date order - finished or needs human check.xlsx
+++ b/12th Senate - audit results/All sittings in date order - finished or needs human check.xlsx
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="K45" s="6" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="L45" s="6" t="n">
         <v>5</v>
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="K52" s="6" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="L52" s="6" t="n">
         <v>1</v>
@@ -3241,7 +3241,7 @@
         </is>
       </c>
       <c r="K53" s="6" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L53" s="6" t="n"/>
       <c r="M53" s="6" t="n">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="K55" s="6" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L55" s="6" t="n">
         <v>4</v>
@@ -3511,7 +3511,7 @@
         </is>
       </c>
       <c r="K58" s="6" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L58" s="6" t="n"/>
       <c r="M58" s="6" t="n"/>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="K64" s="6" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L64" s="6" t="n">
         <v>3</v>
@@ -4151,7 +4151,7 @@
         </is>
       </c>
       <c r="K69" s="6" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L69" s="6" t="n"/>
       <c r="M69" s="6" t="n"/>
@@ -4261,7 +4261,7 @@
         </is>
       </c>
       <c r="K71" s="6" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L71" s="6" t="n"/>
       <c r="M71" s="6" t="n"/>
@@ -4949,7 +4949,7 @@
         </is>
       </c>
       <c r="K83" s="6" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L83" s="6" t="n">
         <v>3</v>
@@ -5121,7 +5121,7 @@
         </is>
       </c>
       <c r="K86" s="6" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L86" s="6" t="n">
         <v>1</v>
@@ -5393,7 +5393,7 @@
         </is>
       </c>
       <c r="K91" s="6" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L91" s="6" t="n"/>
       <c r="M91" s="6" t="n"/>
@@ -5723,7 +5723,7 @@
         </is>
       </c>
       <c r="K97" s="6" t="n">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L97" s="6" t="n">
         <v>1</v>
@@ -5895,7 +5895,7 @@
         </is>
       </c>
       <c r="K100" s="6" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L100" s="6" t="n">
         <v>6</v>
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="K140" s="6" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L140" s="6" t="n">
         <v>1</v>
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="K167" s="6" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L167" s="6" t="n"/>
       <c r="M167" s="6" t="n"/>
@@ -15053,7 +15053,7 @@
         </is>
       </c>
       <c r="K265" s="6" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L265" s="6" t="n"/>
       <c r="M265" s="6" t="n"/>
@@ -15455,7 +15455,7 @@
         </is>
       </c>
       <c r="K272" s="6" t="n">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L272" s="6" t="n">
         <v>9</v>
@@ -17411,7 +17411,7 @@
         </is>
       </c>
       <c r="K307" s="6" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L307" s="6" t="n"/>
       <c r="M307" s="6" t="n"/>
@@ -19433,7 +19433,7 @@
         </is>
       </c>
       <c r="K344" s="6" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L344" s="6" t="n"/>
       <c r="M344" s="6" t="n"/>

--- a/12th Senate - audit results/All sittings in date order - finished or needs human check.xlsx
+++ b/12th Senate - audit results/All sittings in date order - finished or needs human check.xlsx
@@ -3241,7 +3241,7 @@
         </is>
       </c>
       <c r="K53" s="6" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L53" s="6" t="n"/>
       <c r="M53" s="6" t="n">
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="K54" s="6" t="n">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L54" s="6" t="n"/>
       <c r="M54" s="6" t="n"/>
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="K55" s="6" t="n">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L55" s="6" t="n">
         <v>4</v>
@@ -3407,7 +3407,7 @@
         </is>
       </c>
       <c r="K56" s="6" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L56" s="6" t="n"/>
       <c r="M56" s="6" t="n"/>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="K57" s="6" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L57" s="6" t="n"/>
       <c r="M57" s="6" t="n"/>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="K61" s="6" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L61" s="6" t="n">
         <v>3</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="K62" s="6" t="n">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="L62" s="6" t="n">
         <v>1</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="K64" s="6" t="n">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="L64" s="6" t="n">
         <v>3</v>
@@ -3925,7 +3925,7 @@
         </is>
       </c>
       <c r="K65" s="6" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L65" s="6" t="n"/>
       <c r="M65" s="6" t="n"/>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="K67" s="6" t="n">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="L67" s="6" t="n"/>
       <c r="M67" s="6" t="n">
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="K68" s="6" t="n">
-        <v>465</v>
+        <v>453</v>
       </c>
       <c r="L68" s="6" t="n"/>
       <c r="M68" s="6" t="n">
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="K73" s="6" t="n">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="L73" s="6" t="n">
         <v>3</v>
@@ -4551,7 +4551,7 @@
         </is>
       </c>
       <c r="K76" s="6" t="n">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="L76" s="6" t="n"/>
       <c r="M76" s="6" t="n"/>
@@ -4713,7 +4713,7 @@
         </is>
       </c>
       <c r="K79" s="6" t="n">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="L79" s="6" t="n"/>
       <c r="M79" s="6" t="n"/>
@@ -4829,7 +4829,7 @@
         </is>
       </c>
       <c r="K81" s="6" t="n">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="L81" s="6" t="n"/>
       <c r="M81" s="6" t="n"/>
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="K85" s="6" t="n">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="L85" s="6" t="n"/>
       <c r="M85" s="6" t="n"/>
@@ -5229,7 +5229,7 @@
         </is>
       </c>
       <c r="K88" s="6" t="n">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="L88" s="6" t="n"/>
       <c r="M88" s="6" t="n"/>
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="K89" s="6" t="n">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="L89" s="6" t="n">
         <v>5</v>
@@ -5341,7 +5341,7 @@
         </is>
       </c>
       <c r="K90" s="6" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L90" s="6" t="n"/>
       <c r="M90" s="6" t="n"/>
@@ -5393,7 +5393,7 @@
         </is>
       </c>
       <c r="K91" s="6" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="L91" s="6" t="n"/>
       <c r="M91" s="6" t="n"/>
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="K92" s="6" t="n">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="L92" s="6" t="n">
         <v>15</v>
@@ -5723,7 +5723,7 @@
         </is>
       </c>
       <c r="K97" s="6" t="n">
-        <v>489</v>
+        <v>475</v>
       </c>
       <c r="L97" s="6" t="n">
         <v>1</v>
@@ -6129,7 +6129,7 @@
         </is>
       </c>
       <c r="K104" s="6" t="n">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="L104" s="6" t="n"/>
       <c r="M104" s="6" t="n"/>
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="K105" s="6" t="n">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="L105" s="6" t="n"/>
       <c r="M105" s="6" t="n"/>
@@ -6285,7 +6285,7 @@
         </is>
       </c>
       <c r="K107" s="6" t="n">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="L107" s="6" t="n"/>
       <c r="M107" s="6" t="n"/>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="K110" s="6" t="n">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="L110" s="6" t="n"/>
       <c r="M110" s="6" t="n"/>
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="K113" s="6" t="n">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="L113" s="6" t="n"/>
       <c r="M113" s="6" t="n"/>
@@ -6659,7 +6659,7 @@
         </is>
       </c>
       <c r="K114" s="6" t="n">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L114" s="6" t="n"/>
       <c r="M114" s="6" t="n">
@@ -7173,7 +7173,7 @@
         </is>
       </c>
       <c r="K123" s="6" t="n">
-        <v>1469</v>
+        <v>1465</v>
       </c>
       <c r="L123" s="6" t="n"/>
       <c r="M123" s="6" t="n"/>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="K124" s="6" t="n">
-        <v>812</v>
+        <v>780</v>
       </c>
       <c r="L124" s="6" t="n"/>
       <c r="M124" s="6" t="n">
@@ -7349,7 +7349,7 @@
         </is>
       </c>
       <c r="K126" s="6" t="n">
-        <v>542</v>
+        <v>524</v>
       </c>
       <c r="L126" s="6" t="n"/>
       <c r="M126" s="6" t="n">
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="K128" s="6" t="n">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="L128" s="6" t="n"/>
       <c r="M128" s="6" t="n"/>
@@ -7517,7 +7517,7 @@
         </is>
       </c>
       <c r="K129" s="6" t="n">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="L129" s="6" t="n">
         <v>16</v>
@@ -7577,7 +7577,7 @@
         </is>
       </c>
       <c r="K130" s="6" t="n">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="L130" s="6" t="n">
         <v>8</v>
@@ -7693,7 +7693,7 @@
         </is>
       </c>
       <c r="K132" s="6" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L132" s="6" t="n"/>
       <c r="M132" s="6" t="n"/>
@@ -7745,7 +7745,7 @@
         </is>
       </c>
       <c r="K133" s="6" t="n">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="L133" s="6" t="n"/>
       <c r="M133" s="6" t="n"/>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="K134" s="6" t="n">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="L134" s="6" t="n"/>
       <c r="M134" s="6" t="n"/>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="K137" s="6" t="n">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="L137" s="6" t="n"/>
       <c r="M137" s="6" t="n"/>
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="K140" s="6" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="L140" s="6" t="n">
         <v>1</v>
@@ -8369,7 +8369,7 @@
         </is>
       </c>
       <c r="K144" s="6" t="n">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="L144" s="6" t="n"/>
       <c r="M144" s="6" t="n">
@@ -8425,7 +8425,7 @@
         </is>
       </c>
       <c r="K145" s="6" t="n">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="L145" s="6" t="n"/>
       <c r="M145" s="6" t="n"/>
@@ -8639,7 +8639,7 @@
         </is>
       </c>
       <c r="K149" s="6" t="n">
-        <v>472</v>
+        <v>447</v>
       </c>
       <c r="L149" s="6" t="n">
         <v>4</v>
@@ -8803,7 +8803,7 @@
         </is>
       </c>
       <c r="K152" s="6" t="n">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="L152" s="6" t="n"/>
       <c r="M152" s="6" t="n"/>
@@ -8979,7 +8979,7 @@
         </is>
       </c>
       <c r="K155" s="6" t="n">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="L155" s="6" t="n"/>
       <c r="M155" s="6" t="n"/>
@@ -9089,7 +9089,7 @@
         </is>
       </c>
       <c r="K157" s="6" t="n">
-        <v>619</v>
+        <v>583</v>
       </c>
       <c r="L157" s="6" t="n"/>
       <c r="M157" s="6" t="n"/>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="K159" s="6" t="n">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="L159" s="6" t="n"/>
       <c r="M159" s="6" t="n">
@@ -9255,7 +9255,7 @@
         </is>
       </c>
       <c r="K160" s="6" t="n">
-        <v>675</v>
+        <v>649</v>
       </c>
       <c r="L160" s="6" t="n">
         <v>2</v>
@@ -9315,7 +9315,7 @@
         </is>
       </c>
       <c r="K161" s="6" t="n">
-        <v>557</v>
+        <v>547</v>
       </c>
       <c r="L161" s="6" t="n"/>
       <c r="M161" s="6" t="n">
@@ -9599,7 +9599,7 @@
         </is>
       </c>
       <c r="K166" s="6" t="n">
-        <v>585</v>
+        <v>567</v>
       </c>
       <c r="L166" s="6" t="n">
         <v>8</v>
@@ -9765,7 +9765,7 @@
         </is>
       </c>
       <c r="K169" s="6" t="n">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="L169" s="6" t="n"/>
       <c r="M169" s="6" t="n">
@@ -9883,7 +9883,7 @@
         </is>
       </c>
       <c r="K171" s="6" t="n">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="L171" s="6" t="n">
         <v>6</v>
@@ -9939,7 +9939,7 @@
         </is>
       </c>
       <c r="K172" s="6" t="n">
-        <v>445</v>
+        <v>431</v>
       </c>
       <c r="L172" s="6" t="n"/>
       <c r="M172" s="6" t="n"/>
@@ -10115,7 +10115,7 @@
         </is>
       </c>
       <c r="K175" s="6" t="n">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="L175" s="6" t="n">
         <v>1</v>
@@ -10289,7 +10289,7 @@
         </is>
       </c>
       <c r="K178" s="6" t="n">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="L178" s="6" t="n"/>
       <c r="M178" s="6" t="n"/>
@@ -10563,7 +10563,7 @@
         </is>
       </c>
       <c r="K183" s="6" t="n">
-        <v>1234</v>
+        <v>1226</v>
       </c>
       <c r="L183" s="6" t="n"/>
       <c r="M183" s="6" t="n"/>
@@ -11053,7 +11053,7 @@
         </is>
       </c>
       <c r="K192" s="6" t="n">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="L192" s="6" t="n">
         <v>12</v>
@@ -11377,7 +11377,7 @@
         </is>
       </c>
       <c r="K198" s="6" t="n">
-        <v>399</v>
+        <v>381</v>
       </c>
       <c r="L198" s="6" t="n"/>
       <c r="M198" s="6" t="n"/>
@@ -11849,7 +11849,7 @@
         </is>
       </c>
       <c r="K207" s="6" t="n">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L207" s="6" t="n">
         <v>4</v>
@@ -11963,7 +11963,7 @@
         </is>
       </c>
       <c r="K209" s="6" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L209" s="6" t="n">
         <v>15</v>
@@ -12229,7 +12229,7 @@
         </is>
       </c>
       <c r="K214" s="6" t="n">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="L214" s="6" t="n"/>
       <c r="M214" s="6" t="n"/>
@@ -12447,7 +12447,7 @@
         </is>
       </c>
       <c r="K218" s="6" t="n">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="L218" s="6" t="n"/>
       <c r="M218" s="6" t="n"/>
@@ -12895,7 +12895,7 @@
         </is>
       </c>
       <c r="K226" s="6" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="L226" s="6" t="n"/>
       <c r="M226" s="6" t="n"/>
@@ -13369,7 +13369,7 @@
         </is>
       </c>
       <c r="K235" s="6" t="n">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="L235" s="6" t="n"/>
       <c r="M235" s="6" t="n"/>
@@ -13425,7 +13425,7 @@
         </is>
       </c>
       <c r="K236" s="6" t="n">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="L236" s="6" t="n"/>
       <c r="M236" s="6" t="n">
@@ -13531,7 +13531,7 @@
         </is>
       </c>
       <c r="K238" s="6" t="n">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="L238" s="6" t="n"/>
       <c r="M238" s="6" t="n"/>
@@ -14033,7 +14033,7 @@
         </is>
       </c>
       <c r="K247" s="6" t="n">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="L247" s="6" t="n"/>
       <c r="M247" s="6" t="n"/>
@@ -14085,7 +14085,7 @@
         </is>
       </c>
       <c r="K248" s="6" t="n">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="L248" s="6" t="n"/>
       <c r="M248" s="6" t="n"/>
@@ -14415,7 +14415,7 @@
         </is>
       </c>
       <c r="K254" s="6" t="n">
-        <v>446</v>
+        <v>425</v>
       </c>
       <c r="L254" s="6" t="n">
         <v>1</v>
@@ -14697,7 +14697,7 @@
         </is>
       </c>
       <c r="K259" s="6" t="n">
-        <v>382</v>
+        <v>362</v>
       </c>
       <c r="L259" s="6" t="n"/>
       <c r="M259" s="6" t="n">
@@ -14755,7 +14755,7 @@
         </is>
       </c>
       <c r="K260" s="6" t="n">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="L260" s="6" t="n"/>
       <c r="M260" s="6" t="n"/>
@@ -15219,7 +15219,7 @@
         </is>
       </c>
       <c r="K268" s="6" t="n">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="L268" s="6" t="n">
         <v>2</v>
@@ -15455,7 +15455,7 @@
         </is>
       </c>
       <c r="K272" s="6" t="n">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="L272" s="6" t="n">
         <v>9</v>
@@ -15569,7 +15569,7 @@
         </is>
       </c>
       <c r="K274" s="6" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L274" s="6" t="n">
         <v>13</v>
@@ -15625,7 +15625,7 @@
         </is>
       </c>
       <c r="K275" s="6" t="n">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L275" s="6" t="n"/>
       <c r="M275" s="6" t="n"/>
@@ -15677,7 +15677,7 @@
         </is>
       </c>
       <c r="K276" s="6" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L276" s="6" t="n"/>
       <c r="M276" s="6" t="n"/>
@@ -15729,7 +15729,7 @@
         </is>
       </c>
       <c r="K277" s="6" t="n">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="L277" s="6" t="n"/>
       <c r="M277" s="6" t="n"/>
@@ -16643,7 +16643,7 @@
         </is>
       </c>
       <c r="K293" s="6" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="L293" s="6" t="n"/>
       <c r="M293" s="6" t="n"/>
@@ -16865,7 +16865,7 @@
         </is>
       </c>
       <c r="K297" s="6" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L297" s="6" t="n">
         <v>1</v>
@@ -17197,7 +17197,7 @@
         </is>
       </c>
       <c r="K303" s="6" t="n">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="L303" s="6" t="n"/>
       <c r="M303" s="6" t="n"/>
@@ -17467,7 +17467,7 @@
         </is>
       </c>
       <c r="K308" s="6" t="n">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="L308" s="6" t="n">
         <v>5</v>
@@ -17525,7 +17525,7 @@
         </is>
       </c>
       <c r="K309" s="6" t="n">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="L309" s="6" t="n"/>
       <c r="M309" s="6" t="n"/>
@@ -18495,7 +18495,7 @@
         </is>
       </c>
       <c r="K327" s="6" t="n">
-        <v>630</v>
+        <v>610</v>
       </c>
       <c r="L327" s="6" t="n"/>
       <c r="M327" s="6" t="n"/>
@@ -18551,7 +18551,7 @@
         </is>
       </c>
       <c r="K328" s="6" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L328" s="6" t="n"/>
       <c r="M328" s="6" t="n">
@@ -18663,7 +18663,7 @@
         </is>
       </c>
       <c r="K330" s="6" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L330" s="6" t="n"/>
       <c r="M330" s="6" t="n"/>
@@ -18923,7 +18923,7 @@
         </is>
       </c>
       <c r="K335" s="6" t="n">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="L335" s="6" t="n"/>
       <c r="M335" s="6" t="n"/>
@@ -19083,7 +19083,7 @@
         </is>
       </c>
       <c r="K338" s="6" t="n">
-        <v>984</v>
+        <v>968</v>
       </c>
       <c r="L338" s="6" t="n">
         <v>7</v>
@@ -19271,7 +19271,7 @@
         </is>
       </c>
       <c r="K341" s="6" t="n">
-        <v>622</v>
+        <v>587</v>
       </c>
       <c r="L341" s="6" t="n"/>
       <c r="M341" s="6" t="n">
@@ -19377,7 +19377,7 @@
         </is>
       </c>
       <c r="K343" s="6" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L343" s="6" t="n"/>
       <c r="M343" s="6" t="n"/>
@@ -19433,7 +19433,7 @@
         </is>
       </c>
       <c r="K344" s="6" t="n">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="L344" s="6" t="n"/>
       <c r="M344" s="6" t="n"/>
@@ -19545,7 +19545,7 @@
         </is>
       </c>
       <c r="K346" s="6" t="n">
-        <v>547</v>
+        <v>529</v>
       </c>
       <c r="L346" s="6" t="n"/>
       <c r="M346" s="6" t="n"/>
@@ -20341,7 +20341,7 @@
         </is>
       </c>
       <c r="K361" s="6" t="n">
-        <v>916</v>
+        <v>877</v>
       </c>
       <c r="L361" s="6" t="n"/>
       <c r="M361" s="6" t="n">
@@ -20759,7 +20759,7 @@
         </is>
       </c>
       <c r="K369" s="6" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="L369" s="6" t="n"/>
       <c r="M369" s="6" t="n"/>
@@ -21019,7 +21019,7 @@
         </is>
       </c>
       <c r="K374" s="6" t="n">
-        <v>1284</v>
+        <v>1233</v>
       </c>
       <c r="L374" s="6" t="n"/>
       <c r="M374" s="6" t="n"/>
@@ -21229,7 +21229,7 @@
         </is>
       </c>
       <c r="K378" s="6" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="L378" s="6" t="n"/>
       <c r="M378" s="6" t="n"/>
@@ -21337,7 +21337,7 @@
         </is>
       </c>
       <c r="K380" s="6" t="n">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="L380" s="6" t="n"/>
       <c r="M380" s="6" t="n">
@@ -21391,7 +21391,7 @@
         </is>
       </c>
       <c r="K381" s="6" t="n">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="L381" s="6" t="n"/>
       <c r="M381" s="6" t="n"/>
@@ -21807,7 +21807,7 @@
         </is>
       </c>
       <c r="K389" s="6" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L389" s="6" t="n"/>
       <c r="M389" s="6" t="n"/>
@@ -21855,7 +21855,7 @@
         </is>
       </c>
       <c r="K390" s="6" t="n">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="L390" s="6" t="n"/>
       <c r="M390" s="6" t="n"/>
@@ -21903,7 +21903,7 @@
         </is>
       </c>
       <c r="K391" s="6" t="n">
-        <v>375</v>
+        <v>352</v>
       </c>
       <c r="L391" s="6" t="n"/>
       <c r="M391" s="6" t="n"/>
@@ -22107,7 +22107,7 @@
         </is>
       </c>
       <c r="K395" s="6" t="n">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="L395" s="6" t="n"/>
       <c r="M395" s="6" t="n"/>
@@ -22159,7 +22159,7 @@
         </is>
       </c>
       <c r="K396" s="6" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L396" s="6" t="n"/>
       <c r="M396" s="6" t="n"/>
@@ -22385,7 +22385,7 @@
         </is>
       </c>
       <c r="K400" s="6" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L400" s="6" t="n"/>
       <c r="M400" s="6" t="n"/>
@@ -22441,7 +22441,7 @@
         </is>
       </c>
       <c r="K401" s="6" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="L401" s="6" t="n"/>
       <c r="M401" s="6" t="n"/>
@@ -22499,7 +22499,7 @@
         </is>
       </c>
       <c r="K402" s="6" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L402" s="6" t="n"/>
       <c r="M402" s="6" t="n"/>
@@ -22661,7 +22661,7 @@
         </is>
       </c>
       <c r="K405" s="6" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L405" s="6" t="n"/>
       <c r="M405" s="6" t="n"/>
@@ -22717,7 +22717,7 @@
         </is>
       </c>
       <c r="K406" s="6" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L406" s="6" t="n"/>
       <c r="M406" s="6" t="n"/>
@@ -22775,7 +22775,7 @@
         </is>
       </c>
       <c r="K407" s="6" t="n">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="L407" s="6" t="n"/>
       <c r="M407" s="6" t="n">
@@ -22885,7 +22885,7 @@
         </is>
       </c>
       <c r="K409" s="6" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L409" s="6" t="n">
         <v>15</v>
@@ -23045,7 +23045,7 @@
         </is>
       </c>
       <c r="K412" s="6" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L412" s="6" t="n"/>
       <c r="M412" s="6" t="n"/>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="K415" s="6" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L415" s="6" t="n"/>
       <c r="M415" s="6" t="n"/>
@@ -23509,7 +23509,7 @@
         </is>
       </c>
       <c r="K421" s="6" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L421" s="6" t="n"/>
       <c r="M421" s="6" t="n"/>
@@ -23565,7 +23565,7 @@
         </is>
       </c>
       <c r="K422" s="6" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L422" s="6" t="n"/>
       <c r="M422" s="6" t="n"/>
@@ -23623,7 +23623,7 @@
         </is>
       </c>
       <c r="K423" s="6" t="n">
-        <v>683</v>
+        <v>657</v>
       </c>
       <c r="L423" s="6" t="n"/>
       <c r="M423" s="6" t="n">
@@ -23857,7 +23857,7 @@
         </is>
       </c>
       <c r="K427" s="6" t="n">
-        <v>1051</v>
+        <v>1024</v>
       </c>
       <c r="L427" s="6" t="n">
         <v>1</v>
